--- a/Financial Analysis/LDOS.xlsx
+++ b/Financial Analysis/LDOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F88C93-3B59-4FB7-94C1-46DF58F11ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BB1174-692B-45BA-9018-2BDF71FB9367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{0C5083B5-BD04-437F-9545-422299EC636F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>LDOS</t>
   </si>
@@ -194,16 +194,26 @@
   </si>
   <si>
     <t>Slightly overvalued</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +246,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -282,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -301,6 +320,8 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -747,14 +768,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>180.62</v>
+        <v>195.58</v>
       </c>
       <c r="E3" s="4">
-        <v>45898</v>
+        <v>45934</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45898</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="4">
         <v>45965</v>
@@ -777,7 +798,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>23173.546000000002</v>
+        <v>25092.914000000004</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -819,7 +840,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>27347.546000000002</v>
+        <v>29266.914000000004</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +850,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D44293-D96C-4AE6-8EBE-24AD359410D0}">
-  <dimension ref="B2:EM31"/>
+  <dimension ref="B2:EM35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -1142,63 +1163,63 @@
         <v>587</v>
       </c>
       <c r="G5" s="9">
-        <f>G3-G4</f>
+        <f t="shared" ref="G5:L5" si="4">G3-G4</f>
         <v>638</v>
       </c>
       <c r="H5" s="9">
-        <f>H3-H4</f>
+        <f t="shared" si="4"/>
         <v>705</v>
       </c>
       <c r="I5" s="9">
-        <f>I3-I4</f>
+        <f t="shared" si="4"/>
         <v>762</v>
       </c>
       <c r="J5" s="9">
-        <f>J3-J4</f>
+        <f t="shared" si="4"/>
         <v>693</v>
       </c>
       <c r="K5" s="9">
-        <f>K3-K4</f>
+        <f t="shared" si="4"/>
         <v>757</v>
       </c>
       <c r="L5" s="9">
-        <f>L3-L4</f>
+        <f t="shared" si="4"/>
         <v>782</v>
       </c>
       <c r="M5" s="9">
-        <f t="shared" ref="M5:N5" si="4">M3*0.17</f>
+        <f t="shared" ref="M5:N5" si="5">M3*0.17</f>
         <v>762.16100000000006</v>
       </c>
       <c r="N5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>793.99350000000004</v>
       </c>
       <c r="P5" s="9">
-        <f t="shared" ref="P5:V5" si="5">P3-P4</f>
+        <f t="shared" ref="P5:V5" si="6">P3-P4</f>
         <v>1548</v>
       </c>
       <c r="Q5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1737</v>
       </c>
       <c r="R5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2014</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2084</v>
       </c>
       <c r="T5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2244</v>
       </c>
       <c r="U5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2798</v>
       </c>
       <c r="V5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3095.1544999999987</v>
       </c>
       <c r="W5" s="9">
@@ -1206,39 +1227,39 @@
         <v>3521.5440750000002</v>
       </c>
       <c r="X5" s="9">
-        <f t="shared" ref="X5:AF5" si="6">X3*0.19</f>
+        <f t="shared" ref="X5:AF5" si="7">X3*0.19</f>
         <v>3662.4058380000006</v>
       </c>
       <c r="Y5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3772.2780131400004</v>
       </c>
       <c r="Z5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3847.7235734028004</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3924.6780448708569</v>
       </c>
       <c r="AB5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3963.9248253195656</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4003.5640735727611</v>
       </c>
       <c r="AD5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4043.5997143084887</v>
       </c>
       <c r="AE5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4084.0357114515737</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4124.87606856609</v>
       </c>
     </row>
@@ -1262,7 +1283,7 @@
         <v>247</v>
       </c>
       <c r="J6" s="6">
-        <f t="shared" ref="J6:J8" si="7">U6-I6-H6-G6</f>
+        <f t="shared" ref="J6:J8" si="8">U6-I6-H6-G6</f>
         <v>279</v>
       </c>
       <c r="K6" s="6">
@@ -1301,7 +1322,7 @@
         <v>983</v>
       </c>
       <c r="V6" s="6">
-        <f t="shared" ref="V6:V8" si="8">SUM(K6:N6)</f>
+        <f t="shared" ref="V6:V8" si="9">SUM(K6:N6)</f>
         <v>978.26</v>
       </c>
       <c r="W6" s="6">
@@ -1309,19 +1330,19 @@
         <v>997.8252</v>
       </c>
       <c r="X6" s="6">
-        <f t="shared" ref="X6:AF6" si="9">W6*1.02</f>
+        <f t="shared" ref="X6:AA6" si="10">W6*1.02</f>
         <v>1017.781704</v>
       </c>
       <c r="Y6" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1038.1373380800001</v>
       </c>
       <c r="Z6" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1058.9000848416001</v>
       </c>
       <c r="AA6" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1080.0780865384322</v>
       </c>
       <c r="AB6" s="6">
@@ -1329,19 +1350,19 @@
         <v>1090.8788674038165</v>
       </c>
       <c r="AC6" s="6">
-        <f t="shared" ref="AC6:AF6" si="10">AB6*1.01</f>
+        <f t="shared" ref="AC6:AF6" si="11">AB6*1.01</f>
         <v>1101.7876560778545</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1112.8055326386332</v>
       </c>
       <c r="AE6" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1123.9335879650196</v>
       </c>
       <c r="AF6" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1135.1729238446699</v>
       </c>
     </row>
@@ -1365,7 +1386,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="K7" s="6">
@@ -1399,7 +1420,7 @@
         <v>16</v>
       </c>
       <c r="V7" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="W7" s="6">
@@ -1407,39 +1428,39 @@
         <v>14.14</v>
       </c>
       <c r="X7" s="6">
-        <f t="shared" ref="X7:AF7" si="11">W7*1.01</f>
+        <f t="shared" ref="X7:AF7" si="12">W7*1.01</f>
         <v>14.281400000000001</v>
       </c>
       <c r="Y7" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14.424214000000001</v>
       </c>
       <c r="Z7" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14.56845614</v>
       </c>
       <c r="AA7" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14.7141407014</v>
       </c>
       <c r="AB7" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14.861282108414001</v>
       </c>
       <c r="AC7" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.00989492949814</v>
       </c>
       <c r="AD7" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.159993878793122</v>
       </c>
       <c r="AE7" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.311593817581054</v>
       </c>
       <c r="AF7" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.464709755756864</v>
       </c>
     </row>
@@ -1462,7 +1483,7 @@
         <v>6</v>
       </c>
       <c r="J8" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="K8" s="6"/>
@@ -1495,7 +1516,7 @@
         <v>11</v>
       </c>
       <c r="V8" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W8" s="6">
@@ -1562,83 +1583,83 @@
         <v>234</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" ref="L9:N9" si="12">SUM(L6:L8)</f>
+        <f t="shared" ref="L9:N9" si="13">SUM(L6:L8)</f>
         <v>219</v>
       </c>
       <c r="M9" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>253.47</v>
       </c>
       <c r="N9" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>285.79000000000002</v>
       </c>
       <c r="P9" s="6">
-        <f t="shared" ref="P9:W9" si="13">SUM(P6:P8)</f>
+        <f t="shared" ref="P9:W9" si="14">SUM(P6:P8)</f>
         <v>654</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>753</v>
       </c>
       <c r="R9" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>882</v>
       </c>
       <c r="S9" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1008</v>
       </c>
       <c r="T9" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1653</v>
       </c>
       <c r="U9" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1010</v>
       </c>
       <c r="V9" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>992.26</v>
       </c>
       <c r="W9" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1011.9652</v>
       </c>
       <c r="X9" s="6">
-        <f t="shared" ref="X9:AF9" si="14">SUM(X6:X8)</f>
+        <f t="shared" ref="X9:AF9" si="15">SUM(X6:X8)</f>
         <v>1032.0631040000001</v>
       </c>
       <c r="Y9" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1052.56155208</v>
       </c>
       <c r="Z9" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1073.4685409816002</v>
       </c>
       <c r="AA9" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1094.7922272398323</v>
       </c>
       <c r="AB9" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1105.7401495122303</v>
       </c>
       <c r="AC9" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1116.7975510073527</v>
       </c>
       <c r="AD9" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1127.9655265174263</v>
       </c>
       <c r="AE9" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1139.2451817826006</v>
       </c>
       <c r="AF9" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1150.6376336004266</v>
       </c>
     </row>
@@ -1675,83 +1696,83 @@
         <v>523</v>
       </c>
       <c r="L10" s="9">
-        <f t="shared" ref="L10:N10" si="15">L5-L9</f>
+        <f t="shared" ref="L10:N10" si="16">L5-L9</f>
         <v>563</v>
       </c>
       <c r="M10" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>508.69100000000003</v>
       </c>
       <c r="N10" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>508.20350000000002</v>
       </c>
       <c r="P10" s="9">
-        <f t="shared" ref="P10:W10" si="16">P5-P9</f>
+        <f t="shared" ref="P10:W10" si="17">P5-P9</f>
         <v>894</v>
       </c>
       <c r="Q10" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>984</v>
       </c>
       <c r="R10" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1132</v>
       </c>
       <c r="S10" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1076</v>
       </c>
       <c r="T10" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>591</v>
       </c>
       <c r="U10" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1788</v>
       </c>
       <c r="V10" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2102.8944999999985</v>
       </c>
       <c r="W10" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2509.5788750000002</v>
       </c>
       <c r="X10" s="9">
-        <f t="shared" ref="X10:AF10" si="17">X5-X9</f>
+        <f t="shared" ref="X10:AF10" si="18">X5-X9</f>
         <v>2630.3427340000007</v>
       </c>
       <c r="Y10" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2719.7164610600003</v>
       </c>
       <c r="Z10" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2774.2550324212002</v>
       </c>
       <c r="AA10" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2829.8858176310246</v>
       </c>
       <c r="AB10" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2858.1846758073352</v>
       </c>
       <c r="AC10" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2886.7665225654082</v>
       </c>
       <c r="AD10" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2915.6341877910627</v>
       </c>
       <c r="AE10" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2944.7905296689732</v>
       </c>
       <c r="AF10" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2974.2384349656631</v>
       </c>
     </row>
@@ -1775,7 +1796,7 @@
         <v>-10</v>
       </c>
       <c r="J11" s="6">
-        <f t="shared" ref="J11:J12" si="18">U11-I11-H11-G11</f>
+        <f t="shared" ref="J11:J12" si="19">U11-I11-H11-G11</f>
         <v>-14</v>
       </c>
       <c r="K11" s="6">
@@ -1785,11 +1806,11 @@
         <v>-8</v>
       </c>
       <c r="M11" s="6">
-        <f t="shared" ref="M11:N11" si="19">I11*1.03</f>
+        <f t="shared" ref="M11:N11" si="20">I11*1.03</f>
         <v>-10.3</v>
       </c>
       <c r="N11" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-14.42</v>
       </c>
       <c r="P11" s="6">
@@ -1811,7 +1832,7 @@
         <v>-39</v>
       </c>
       <c r="V11" s="6">
-        <f t="shared" ref="V11:V13" si="20">SUM(K11:N11)</f>
+        <f t="shared" ref="V11:V13" si="21">SUM(K11:N11)</f>
         <v>-39.72</v>
       </c>
       <c r="W11" s="6">
@@ -1819,39 +1840,39 @@
         <v>-40.9116</v>
       </c>
       <c r="X11" s="6">
-        <f t="shared" ref="X11:AF11" si="21">W11*1.03</f>
+        <f t="shared" ref="X11:AF11" si="22">W11*1.03</f>
         <v>-42.138947999999999</v>
       </c>
       <c r="Y11" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-43.403116439999998</v>
       </c>
       <c r="Z11" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-44.705209933200003</v>
       </c>
       <c r="AA11" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-46.046366231196004</v>
       </c>
       <c r="AB11" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-47.427757218131887</v>
       </c>
       <c r="AC11" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-48.850589934675845</v>
       </c>
       <c r="AD11" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-50.316107632716125</v>
       </c>
       <c r="AE11" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-51.825590861697613</v>
       </c>
       <c r="AF11" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-53.380358587548542</v>
       </c>
     </row>
@@ -1875,7 +1896,7 @@
         <v>46</v>
       </c>
       <c r="J12" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>47</v>
       </c>
       <c r="K12" s="6">
@@ -1909,7 +1930,7 @@
         <v>193</v>
       </c>
       <c r="V12" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>204</v>
       </c>
       <c r="W12" s="6">
@@ -1917,39 +1938,39 @@
         <v>210.12</v>
       </c>
       <c r="X12" s="6">
-        <f t="shared" ref="X12:AF12" si="22">W12*1.03</f>
+        <f t="shared" ref="X12:AF12" si="23">W12*1.03</f>
         <v>216.42360000000002</v>
       </c>
       <c r="Y12" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>222.91630800000001</v>
       </c>
       <c r="Z12" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>229.60379724000003</v>
       </c>
       <c r="AA12" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>236.49191115720004</v>
       </c>
       <c r="AB12" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>243.58666849191604</v>
       </c>
       <c r="AC12" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>250.89426854667354</v>
       </c>
       <c r="AD12" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>258.42109660307375</v>
       </c>
       <c r="AE12" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>266.17372950116595</v>
       </c>
       <c r="AF12" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>274.15894138620092</v>
       </c>
     </row>
@@ -2007,7 +2028,7 @@
         <v>-5</v>
       </c>
       <c r="V13" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="W13" s="6">
@@ -2054,103 +2075,103 @@
         <v>44</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" ref="G14:L14" si="23">SUM(G11:G13)</f>
+        <f t="shared" ref="G14:L14" si="24">SUM(G11:G13)</f>
         <v>40</v>
       </c>
       <c r="H14" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>41</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>36</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>32</v>
       </c>
       <c r="K14" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>45</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>45</v>
       </c>
       <c r="M14" s="6">
-        <f t="shared" ref="M14:N14" si="24">SUM(M11:M13)</f>
+        <f t="shared" ref="M14:N14" si="25">SUM(M11:M13)</f>
         <v>39.700000000000003</v>
       </c>
       <c r="N14" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>35.58</v>
       </c>
       <c r="P14" s="6">
-        <f t="shared" ref="P14:W14" si="25">SUM(P11:P13)</f>
+        <f t="shared" ref="P14:W14" si="26">SUM(P11:P13)</f>
         <v>28</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>203</v>
       </c>
       <c r="R14" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>165</v>
       </c>
       <c r="S14" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>190</v>
       </c>
       <c r="T14" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>188</v>
       </c>
       <c r="U14" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>149</v>
       </c>
       <c r="V14" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>165.28</v>
       </c>
       <c r="W14" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>169.20840000000001</v>
       </c>
       <c r="X14" s="6">
-        <f t="shared" ref="X14:AF14" si="26">SUM(X11:X13)</f>
+        <f t="shared" ref="X14:AF14" si="27">SUM(X11:X13)</f>
         <v>174.28465200000002</v>
       </c>
       <c r="Y14" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>179.51319156000002</v>
       </c>
       <c r="Z14" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>184.89858730680004</v>
       </c>
       <c r="AA14" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>190.44554492600403</v>
       </c>
       <c r="AB14" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>196.15891127378416</v>
       </c>
       <c r="AC14" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>202.04367861199771</v>
       </c>
       <c r="AD14" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>208.10498897035762</v>
       </c>
       <c r="AE14" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>214.34813863946835</v>
       </c>
       <c r="AF14" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>220.77858279865239</v>
       </c>
     </row>
@@ -2167,103 +2188,103 @@
         <v>-388</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" ref="G15:L15" si="27">G10-G14</f>
+        <f t="shared" ref="G15:L15" si="28">G10-G14</f>
         <v>368</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>426</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>470</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>375</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>478</v>
       </c>
       <c r="L15" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>518</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" ref="M15:N15" si="28">M10-M14</f>
+        <f t="shared" ref="M15:N15" si="29">M10-M14</f>
         <v>468.99100000000004</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>472.62350000000004</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" ref="P15:W15" si="29">P10-P14</f>
+        <f t="shared" ref="P15:W15" si="30">P10-P14</f>
         <v>866</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>781</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>967</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>886</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>403</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1639</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1937.6144999999985</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2340.3704750000002</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" ref="X15:AF15" si="30">X10-X14</f>
+        <f t="shared" ref="X15:AF15" si="31">X10-X14</f>
         <v>2456.0580820000009</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2540.2032695000003</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2589.3564451144002</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2639.4402727050206</v>
       </c>
       <c r="AB15" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2662.025764533551</v>
       </c>
       <c r="AC15" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2684.7228439534106</v>
       </c>
       <c r="AD15" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2707.529198820705</v>
       </c>
       <c r="AE15" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2730.442391029505</v>
       </c>
       <c r="AF15" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2753.4598521670109</v>
       </c>
     </row>
@@ -2287,7 +2308,7 @@
         <v>108</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" ref="J16:J17" si="31">U16-I16-H16-G16</f>
+        <f t="shared" ref="J16:J17" si="32">U16-I16-H16-G16</f>
         <v>93</v>
       </c>
       <c r="K16" s="6">
@@ -2297,11 +2318,11 @@
         <v>125</v>
       </c>
       <c r="M16" s="6">
-        <f t="shared" ref="M16:N16" si="32">M15*0.22</f>
+        <f t="shared" ref="M16:N16" si="33">M15*0.22</f>
         <v>103.17802</v>
       </c>
       <c r="N16" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>103.97717000000002</v>
       </c>
       <c r="P16" s="6">
@@ -2323,7 +2344,7 @@
         <v>388</v>
       </c>
       <c r="V16" s="6">
-        <f t="shared" ref="V16:V17" si="33">SUM(K16:N16)</f>
+        <f t="shared" ref="V16:V17" si="34">SUM(K16:N16)</f>
         <v>445.15519</v>
       </c>
       <c r="W16" s="6">
@@ -2331,39 +2352,39 @@
         <v>514.88150450000001</v>
       </c>
       <c r="X16" s="6">
-        <f t="shared" ref="X16:AF16" si="34">X15*0.22</f>
+        <f t="shared" ref="X16:AF16" si="35">X15*0.22</f>
         <v>540.33277804000022</v>
       </c>
       <c r="Y16" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>558.84471929000006</v>
       </c>
       <c r="Z16" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>569.65841792516801</v>
       </c>
       <c r="AA16" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>580.67685999510456</v>
       </c>
       <c r="AB16" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>585.64566819738127</v>
       </c>
       <c r="AC16" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>590.63902566975037</v>
       </c>
       <c r="AD16" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>595.65642374055506</v>
       </c>
       <c r="AE16" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>600.69732602649106</v>
       </c>
       <c r="AF16" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>605.76116747674246</v>
       </c>
     </row>
@@ -2387,7 +2408,7 @@
         <v>-2</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-2</v>
       </c>
       <c r="K17" s="6">
@@ -2421,7 +2442,7 @@
         <v>-3</v>
       </c>
       <c r="V17" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4</v>
       </c>
       <c r="W17" s="6">
@@ -2468,103 +2489,103 @@
         <v>-399</v>
       </c>
       <c r="G18" s="9">
-        <f t="shared" ref="G18:L18" si="35">G15-G16-G17</f>
+        <f t="shared" ref="G18:L18" si="36">G15-G16-G17</f>
         <v>284</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>322</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>364</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>284</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>363</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>391</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" ref="M18:N18" si="36">M15-M16-M17</f>
+        <f t="shared" ref="M18:N18" si="37">M15-M16-M17</f>
         <v>365.81298000000004</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>368.64633000000003</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" ref="P18:W18" si="37">P15-P16-P17</f>
+        <f t="shared" ref="P18:W18" si="38">P15-P16-P17</f>
         <v>667</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>628</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>753</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>685</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>199</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1254</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1488.4593099999986</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1825.4889705000001</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" ref="X18:AF18" si="38">X15-X16-X17</f>
+        <f t="shared" ref="X18:AF18" si="39">X15-X16-X17</f>
         <v>1915.7253039600007</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1981.3585502100002</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2019.6980271892321</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2058.7634127099159</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2076.3800963361696</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2094.0838182836601</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2111.8727750801499</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2129.7450650030141</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2147.6986846902682</v>
       </c>
       <c r="AG18" s="2">
@@ -2572,443 +2593,443 @@
         <v>2126.2216978433657</v>
       </c>
       <c r="AH18" s="2">
-        <f t="shared" ref="AH18:CS18" si="39">AG18*(1+$AI$23)</f>
+        <f t="shared" ref="AH18:CS18" si="40">AG18*(1+$AI$23)</f>
         <v>2104.9594808649322</v>
       </c>
       <c r="AI18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2083.9098860562826</v>
       </c>
       <c r="AJ18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2063.0707871957197</v>
       </c>
       <c r="AK18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2042.4400793237626</v>
       </c>
       <c r="AL18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2022.0156785305248</v>
       </c>
       <c r="AM18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2001.7955217452195</v>
       </c>
       <c r="AN18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1981.7775665277672</v>
       </c>
       <c r="AO18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1961.9597908624896</v>
       </c>
       <c r="AP18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1942.3401929538647</v>
       </c>
       <c r="AQ18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1922.9167910243261</v>
       </c>
       <c r="AR18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1903.687623114083</v>
       </c>
       <c r="AS18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1884.650746882942</v>
       </c>
       <c r="AT18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1865.8042394141125</v>
       </c>
       <c r="AU18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1847.1461970199714</v>
       </c>
       <c r="AV18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1828.6747350497717</v>
       </c>
       <c r="AW18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1810.3879876992739</v>
       </c>
       <c r="AX18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1792.2841078222812</v>
       </c>
       <c r="AY18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1774.3612667440584</v>
       </c>
       <c r="AZ18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1756.6176540766178</v>
       </c>
       <c r="BA18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1739.0514775358515</v>
       </c>
       <c r="BB18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1721.660962760493</v>
       </c>
       <c r="BC18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1704.4443531328882</v>
       </c>
       <c r="BD18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1687.3999096015593</v>
       </c>
       <c r="BE18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1670.5259105055438</v>
       </c>
       <c r="BF18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1653.8206514004885</v>
       </c>
       <c r="BG18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1637.2824448864835</v>
       </c>
       <c r="BH18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1620.9096204376187</v>
       </c>
       <c r="BI18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1604.7005242332425</v>
       </c>
       <c r="BJ18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1588.65351899091</v>
       </c>
       <c r="BK18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1572.7669838010008</v>
       </c>
       <c r="BL18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1557.0393139629907</v>
       </c>
       <c r="BM18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1541.4689208233608</v>
       </c>
       <c r="BN18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1526.0542316151273</v>
       </c>
       <c r="BO18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1510.793689298976</v>
       </c>
       <c r="BP18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1495.6857524059862</v>
       </c>
       <c r="BQ18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1480.7288948819264</v>
       </c>
       <c r="BR18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1465.9216059331072</v>
       </c>
       <c r="BS18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1451.2623898737761</v>
       </c>
       <c r="BT18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1436.7497659750384</v>
       </c>
       <c r="BU18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1422.382268315288</v>
       </c>
       <c r="BV18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1408.158445632135</v>
       </c>
       <c r="BW18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1394.0768611758137</v>
       </c>
       <c r="BX18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1380.1360925640556</v>
       </c>
       <c r="BY18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1366.334731638415</v>
       </c>
       <c r="BZ18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1352.6713843220307</v>
       </c>
       <c r="CA18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1339.1446704788104</v>
       </c>
       <c r="CB18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1325.7532237740222</v>
       </c>
       <c r="CC18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1312.495691536282</v>
       </c>
       <c r="CD18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1299.3707346209192</v>
       </c>
       <c r="CE18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1286.3770272747099</v>
       </c>
       <c r="CF18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1273.5132570019628</v>
       </c>
       <c r="CG18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1260.7781244319431</v>
       </c>
       <c r="CH18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1248.1703431876235</v>
       </c>
       <c r="CI18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1235.6886397557473</v>
       </c>
       <c r="CJ18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1223.3317533581899</v>
       </c>
       <c r="CK18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1211.098435824608</v>
       </c>
       <c r="CL18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1198.987451466362</v>
       </c>
       <c r="CM18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1186.9975769516984</v>
       </c>
       <c r="CN18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1175.1276011821815</v>
       </c>
       <c r="CO18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1163.3763251703597</v>
       </c>
       <c r="CP18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1151.7425619186561</v>
       </c>
       <c r="CQ18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1140.2251362994696</v>
       </c>
       <c r="CR18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1128.8228849364748</v>
       </c>
       <c r="CS18" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1117.5346560871101</v>
       </c>
       <c r="CT18" s="2">
-        <f t="shared" ref="CT18:EM18" si="40">CS18*(1+$AI$23)</f>
+        <f t="shared" ref="CT18:EM18" si="41">CS18*(1+$AI$23)</f>
         <v>1106.359309526239</v>
       </c>
       <c r="CU18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1095.2957164309767</v>
       </c>
       <c r="CV18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1084.3427592666669</v>
       </c>
       <c r="CW18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1073.4993316740001</v>
       </c>
       <c r="CX18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1062.7643383572602</v>
       </c>
       <c r="CY18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1052.1366949736876</v>
       </c>
       <c r="CZ18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1041.6153280239507</v>
       </c>
       <c r="DA18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1031.1991747437112</v>
       </c>
       <c r="DB18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1020.8871829962741</v>
       </c>
       <c r="DC18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1010.6783111663113</v>
       </c>
       <c r="DD18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1000.5715280546482</v>
       </c>
       <c r="DE18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>990.56581277410169</v>
       </c>
       <c r="DF18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>980.66015464636064</v>
       </c>
       <c r="DG18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>970.853553099897</v>
       </c>
       <c r="DH18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>961.14501756889797</v>
       </c>
       <c r="DI18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>951.53356739320895</v>
       </c>
       <c r="DJ18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>942.01823171927686</v>
       </c>
       <c r="DK18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>932.59804940208403</v>
       </c>
       <c r="DL18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>923.27206890806315</v>
       </c>
       <c r="DM18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>914.03934821898247</v>
       </c>
       <c r="DN18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>904.89895473679269</v>
       </c>
       <c r="DO18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>895.84996518942478</v>
       </c>
       <c r="DP18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>886.89146553753051</v>
       </c>
       <c r="DQ18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>878.0225508821552</v>
       </c>
       <c r="DR18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>869.24232537333364</v>
       </c>
       <c r="DS18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>860.54990211960035</v>
       </c>
       <c r="DT18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>851.94440309840434</v>
       </c>
       <c r="DU18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>843.42495906742033</v>
       </c>
       <c r="DV18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>834.99070947674613</v>
       </c>
       <c r="DW18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>826.64080238197869</v>
       </c>
       <c r="DX18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>818.37439435815884</v>
       </c>
       <c r="DY18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>810.19065041457725</v>
       </c>
       <c r="DZ18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>802.0887439104315</v>
       </c>
       <c r="EA18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>794.06785647132722</v>
       </c>
       <c r="EB18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>786.12717790661395</v>
       </c>
       <c r="EC18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>778.26590612754785</v>
       </c>
       <c r="ED18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>770.48324706627238</v>
       </c>
       <c r="EE18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>762.77841459560966</v>
       </c>
       <c r="EF18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>755.15063044965359</v>
       </c>
       <c r="EG18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>747.59912414515702</v>
       </c>
       <c r="EH18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>740.12313290370548</v>
       </c>
       <c r="EI18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>732.72190157466844</v>
       </c>
       <c r="EJ18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>725.39468255892177</v>
       </c>
       <c r="EK18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>718.14073573333258</v>
       </c>
       <c r="EL18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>710.95932837599923</v>
       </c>
       <c r="EM18" s="2">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>703.84973509223926</v>
       </c>
     </row>
@@ -3025,103 +3046,103 @@
         <v>128.69999999999999</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" ref="G19:L19" si="41">128.7</f>
+        <f t="shared" ref="G19:L19" si="42">128.7</f>
         <v>128.69999999999999</v>
       </c>
       <c r="H19" s="6">
-        <f t="shared" si="41"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="I19" s="6">
-        <f t="shared" si="41"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="J19" s="6">
-        <f t="shared" si="41"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="K19" s="6">
-        <f t="shared" si="41"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="L19" s="6">
-        <f t="shared" si="41"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="M19" s="6">
-        <f t="shared" ref="M19:N19" si="42">128.7</f>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="N19" s="6">
         <f t="shared" si="42"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="P19" s="6">
-        <f t="shared" ref="P19:W19" si="43">128.7</f>
+      <c r="I19" s="6">
+        <f t="shared" si="42"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="Q19" s="6">
+      <c r="J19" s="6">
+        <f t="shared" si="42"/>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="K19" s="6">
+        <f t="shared" si="42"/>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="L19" s="6">
+        <f t="shared" si="42"/>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="M19" s="6">
+        <f t="shared" ref="M19:N19" si="43">128.7</f>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="N19" s="6">
         <f t="shared" si="43"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="R19" s="6">
-        <f t="shared" si="43"/>
+      <c r="P19" s="6">
+        <f t="shared" ref="P19:W19" si="44">128.7</f>
         <v>128.69999999999999</v>
       </c>
-      <c r="S19" s="6">
-        <f t="shared" si="43"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="T19" s="6">
-        <f t="shared" si="43"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="U19" s="6">
-        <f t="shared" si="43"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="V19" s="6">
-        <f t="shared" si="43"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="W19" s="6">
-        <f t="shared" si="43"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="X19" s="6">
-        <f t="shared" ref="X19:AF19" si="44">128.7</f>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="Y19" s="6">
+      <c r="Q19" s="6">
         <f t="shared" si="44"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="Z19" s="6">
+      <c r="R19" s="6">
         <f t="shared" si="44"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="AA19" s="6">
+      <c r="S19" s="6">
         <f t="shared" si="44"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="AB19" s="6">
+      <c r="T19" s="6">
         <f t="shared" si="44"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="AC19" s="6">
+      <c r="U19" s="6">
         <f t="shared" si="44"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="AD19" s="6">
+      <c r="V19" s="6">
         <f t="shared" si="44"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="AE19" s="6">
+      <c r="W19" s="6">
         <f t="shared" si="44"/>
         <v>128.69999999999999</v>
       </c>
+      <c r="X19" s="6">
+        <f t="shared" ref="X19:AF19" si="45">128.7</f>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="Y19" s="6">
+        <f t="shared" si="45"/>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="Z19" s="6">
+        <f t="shared" si="45"/>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="AA19" s="6">
+        <f t="shared" si="45"/>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="AB19" s="6">
+        <f t="shared" si="45"/>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="AC19" s="6">
+        <f t="shared" si="45"/>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="AD19" s="6">
+        <f t="shared" si="45"/>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="AE19" s="6">
+        <f t="shared" si="45"/>
+        <v>128.69999999999999</v>
+      </c>
       <c r="AF19" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>128.69999999999999</v>
       </c>
     </row>
@@ -3138,103 +3159,103 @@
         <v>-3.1002331002331007</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" ref="G20:L20" si="45">G18/G19</f>
+        <f t="shared" ref="G20:L20" si="46">G18/G19</f>
         <v>2.2066822066822067</v>
       </c>
       <c r="H20" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.5019425019425023</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.8282828282828287</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.2066822066822067</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.8205128205128207</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>3.0380730380730383</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" ref="M20:N20" si="46">M18/M19</f>
+        <f t="shared" ref="M20:N20" si="47">M18/M19</f>
         <v>2.8423696969696977</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2.8643848484848489</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" ref="P20:W20" si="47">P18/P19</f>
+        <f t="shared" ref="P20:W20" si="48">P18/P19</f>
         <v>5.1825951825951835</v>
       </c>
       <c r="Q20" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>4.8795648795648798</v>
       </c>
       <c r="R20" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.8508158508158514</v>
       </c>
       <c r="S20" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.3224553224553226</v>
       </c>
       <c r="T20" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1.5462315462315463</v>
       </c>
       <c r="U20" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>9.7435897435897445</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>11.565340404040395</v>
       </c>
       <c r="W20" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>14.184063484848487</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" ref="X20:AF20" si="48">X18/X19</f>
+        <f t="shared" ref="X20:AF20" si="49">X18/X19</f>
         <v>14.885200496969704</v>
       </c>
       <c r="Y20" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>15.395171330303032</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>15.693069364329698</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>15.996607713363762</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>16.13348948202152</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>16.271047539111578</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>16.409267871640637</v>
       </c>
       <c r="AE20" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>16.548135703209123</v>
       </c>
       <c r="AF20" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>16.687635467678852</v>
       </c>
     </row>
@@ -3247,11 +3268,11 @@
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10">
-        <f t="shared" ref="H22:I22" si="49">H3/D3-1</f>
+        <f t="shared" ref="H22:I22" si="50">H3/D3-1</f>
         <v>7.6602397081813489E-2</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>6.8604947717419096E-2</v>
       </c>
       <c r="J22" s="10"/>
@@ -3260,15 +3281,15 @@
         <v>6.7924528301886777E-2</v>
       </c>
       <c r="L22" s="10">
-        <f t="shared" ref="L22:N22" si="50">L3/H3-1</f>
+        <f t="shared" ref="L22:N22" si="51">L3/H3-1</f>
         <v>2.9283639883833423E-2</v>
       </c>
       <c r="M22" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="P22" s="10"/>
@@ -3277,63 +3298,63 @@
         <v>0.10843699296917242</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" ref="R22:AF22" si="51">R3/Q3-1</f>
+        <f t="shared" ref="R22:AF22" si="52">R3/Q3-1</f>
         <v>0.11710173212978781</v>
       </c>
       <c r="S22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>4.797262866710339E-2</v>
       </c>
       <c r="T22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>7.2381217004723553E-2</v>
       </c>
       <c r="U22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>7.9284881461329171E-2</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>5.9407634137558452E-2</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -3342,28 +3363,28 @@
         <v>41</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" ref="D23:J23" si="52">D5/D3</f>
+        <f t="shared" ref="D23:J23" si="53">D5/D3</f>
         <v>0.14773319437206878</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.14970670747258352</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.16050314465408805</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.17061955469506293</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.18186157517899762</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.15876288659793814</v>
       </c>
       <c r="K23" s="10">
@@ -3371,15 +3392,15 @@
         <v>0.17832744405182568</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" ref="L23:N23" si="53">L5/L3</f>
+        <f t="shared" ref="L23:N23" si="54">L5/L3</f>
         <v>0.1838702092640489</v>
       </c>
       <c r="M23" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.17</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.17</v>
       </c>
       <c r="P23" s="10">
@@ -3391,63 +3412,63 @@
         <v>0.14125396438155649</v>
       </c>
       <c r="R23" s="10">
-        <f t="shared" ref="R23:AF23" si="54">R5/R3</f>
+        <f t="shared" ref="R23:AF23" si="55">R5/R3</f>
         <v>0.14661134163208853</v>
       </c>
       <c r="S23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.14476243400944708</v>
       </c>
       <c r="T23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.14535561601243685</v>
       </c>
       <c r="U23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.16792701956547834</v>
       </c>
       <c r="V23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.17534448230638708</v>
       </c>
       <c r="W23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.19</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.19</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.19</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.19</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.19</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.19</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.19</v>
       </c>
       <c r="AD23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.19</v>
       </c>
       <c r="AE23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.19</v>
       </c>
       <c r="AF23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.19000000000000003</v>
       </c>
       <c r="AH23" s="1" t="s">
@@ -3466,11 +3487,11 @@
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10">
-        <f t="shared" ref="H24:I24" si="55">H6/D6-1</f>
+        <f t="shared" ref="H24:I24" si="56">H6/D6-1</f>
         <v>-2.5316455696202556E-2</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>3.3472803347280422E-2</v>
       </c>
       <c r="J24" s="10"/>
@@ -3479,15 +3500,15 @@
         <v>1.7699115044247815E-2</v>
       </c>
       <c r="L24" s="10">
-        <f t="shared" ref="L24:N24" si="56">L6/H6-1</f>
+        <f t="shared" ref="L24:N24" si="57">L6/H6-1</f>
         <v>-6.0606060606060552E-2</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="N24" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="P24" s="10"/>
@@ -3496,63 +3517,63 @@
         <v>8.1664098613251079E-2</v>
       </c>
       <c r="R24" s="10">
-        <f t="shared" ref="R24:AF24" si="57">R6/Q6-1</f>
+        <f t="shared" ref="R24:AF24" si="58">R6/Q6-1</f>
         <v>0.21225071225071224</v>
       </c>
       <c r="S24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.11750881316098716</v>
       </c>
       <c r="T24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>-9.4637223974763929E-3</v>
       </c>
       <c r="U24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>4.3524416135881205E-2</v>
       </c>
       <c r="V24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>-4.8219735503560734E-3</v>
       </c>
       <c r="W24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Y24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Z24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AC24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF24" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH24" s="1" t="s">
@@ -3567,28 +3588,28 @@
         <v>43</v>
       </c>
       <c r="D25" s="10">
-        <f t="shared" ref="D25:J25" si="58">D6/D3</f>
+        <f t="shared" ref="D25:J25" si="59">D6/D3</f>
         <v>6.175091193329859E-2</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6.0953838306554452E-2</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>5.6855345911949684E-2</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>5.5905130687318491E-2</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>5.8949880668257758E-2</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6.3917525773195871E-2</v>
       </c>
       <c r="K25" s="10">
@@ -3596,15 +3617,15 @@
         <v>5.418138987043581E-2</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" ref="L25:N25" si="59">L6/L3</f>
+        <f t="shared" ref="L25:N25" si="60">L6/L3</f>
         <v>5.1022807430049374E-2</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>5.5644279883121803E-2</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>6.033336544946527E-2</v>
       </c>
       <c r="P25" s="10">
@@ -3616,63 +3637,63 @@
         <v>5.7087094413271533E-2</v>
       </c>
       <c r="R25" s="10">
-        <f t="shared" ref="R25:AF25" si="60">R6/R3</f>
+        <f t="shared" ref="R25:AF25" si="61">R6/R3</f>
         <v>6.1949479507898378E-2</v>
       </c>
       <c r="S25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>6.6060016671297586E-2</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>6.1018266614846481E-2</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.8996519025327092E-2</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.5419686888343152E-2</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.3836267262961909E-2</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.2800954430981872E-2</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.2288323805438366E-2</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.2288323805438366E-2</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.2288323805438366E-2</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.228832380543836E-2</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.228832380543836E-2</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.228832380543836E-2</v>
       </c>
       <c r="AE25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.2288323805438366E-2</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5.2288323805438366E-2</v>
       </c>
       <c r="AH25" s="1" t="s">
@@ -3688,28 +3709,28 @@
         <v>44</v>
       </c>
       <c r="D26" s="10">
-        <f t="shared" ref="D26:J26" si="61">D10/D3</f>
+        <f t="shared" ref="D26:J26" si="62">D10/D3</f>
         <v>8.4418968212610732E-2</v>
       </c>
       <c r="E26" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-8.7732721244580467E-2</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.10264150943396226</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.11302032913843175</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.12076372315035799</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>9.3241695303550975E-2</v>
       </c>
       <c r="K26" s="10">
@@ -3717,15 +3738,15 @@
         <v>0.1232037691401649</v>
       </c>
       <c r="L26" s="10">
-        <f t="shared" ref="L26:N26" si="62">L10/L3</f>
+        <f t="shared" ref="L26:N26" si="63">L10/L3</f>
         <v>0.13237714554432164</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.11346352017487119</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.10881020436565286</v>
       </c>
       <c r="P26" s="10">
@@ -3737,63 +3758,63 @@
         <v>8.0019516955354961E-2</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" ref="R26:AF26" si="63">R10/R3</f>
+        <f t="shared" ref="R26:AF26" si="64">R10/R3</f>
         <v>8.2405183082186792E-2</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>7.4742984162267295E-2</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>3.8282160901671199E-2</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.10731004681310767</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.11913167741624808</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.13540082875435827</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.13645814843199255</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.13698516540971131</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.13699228806446473</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.1369993408892696</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.13699934088926963</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.1369993408892696</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.13699934088926963</v>
       </c>
       <c r="AE26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.13699934088926963</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.13699934088926963</v>
       </c>
       <c r="AH26" s="1" t="s">
@@ -3809,28 +3830,28 @@
         <v>34</v>
       </c>
       <c r="D27" s="10">
-        <f t="shared" ref="D27:J27" si="64">D16/D15</f>
+        <f t="shared" ref="D27:J27" si="65">D16/D15</f>
         <v>0.23357664233576642</v>
       </c>
       <c r="E27" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>-2.0618556701030927E-2</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.23097826086956522</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.23943661971830985</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.22978723404255319</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.248</v>
       </c>
       <c r="K27" s="10">
@@ -3838,15 +3859,15 @@
         <v>0.23640167364016737</v>
       </c>
       <c r="L27" s="10">
-        <f t="shared" ref="L27:N27" si="65">L16/L15</f>
+        <f t="shared" ref="L27:N27" si="66">L16/L15</f>
         <v>0.2413127413127413</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.22</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.22000000000000003</v>
       </c>
       <c r="P27" s="10">
@@ -3858,63 +3879,63 @@
         <v>0.1946222791293214</v>
       </c>
       <c r="R27" s="10">
-        <f t="shared" ref="R27:AF27" si="66">R16/R15</f>
+        <f t="shared" ref="R27:AF27" si="67">R16/R15</f>
         <v>0.21509824198552224</v>
       </c>
       <c r="S27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.21783295711060949</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.4838709677419355</v>
       </c>
       <c r="U27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.23672971323978034</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.22974394029359316</v>
       </c>
       <c r="W27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="X27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.22</v>
       </c>
       <c r="Y27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.22</v>
       </c>
       <c r="Z27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.22000000000000003</v>
       </c>
       <c r="AB27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.22000000000000003</v>
       </c>
       <c r="AC27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.22000000000000003</v>
       </c>
       <c r="AD27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="AE27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="AF27" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.22000000000000003</v>
       </c>
       <c r="AH27" s="1" t="s">
@@ -3930,28 +3951,28 @@
         <v>45</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" ref="D28:J28" si="67">D18/D3</f>
+        <f t="shared" ref="D28:J28" si="68">D18/D3</f>
         <v>5.3934340802501306E-2</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>-0.10175975516449885</v>
       </c>
       <c r="F28" s="10"/>
       <c r="G28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>7.1446540880503145E-2</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>7.7928363988383348E-2</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>8.6873508353221954E-2</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>6.5063001145475377E-2</v>
       </c>
       <c r="K28" s="10">
@@ -3959,15 +3980,15 @@
         <v>8.5512367491166072E-2</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" ref="L28:N28" si="68">L18/L3</f>
+        <f t="shared" ref="L28:N28" si="69">L18/L3</f>
         <v>9.193510463202445E-2</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>8.159457988535232E-2</v>
       </c>
       <c r="N28" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>7.8929961139480365E-2</v>
       </c>
       <c r="P28" s="10">
@@ -3979,63 +4000,63 @@
         <v>5.1069366512157439E-2</v>
       </c>
       <c r="R28" s="10">
-        <f t="shared" ref="R28:AF28" si="69">R18/R3</f>
+        <f t="shared" ref="R28:AF28" si="70">R18/R3</f>
         <v>5.4815461891242631E-2</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>4.7582661850514033E-2</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1.28902707604612E-2</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7.5261073100468132E-2</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8.4323133835830164E-2</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.8491711876416033E-2</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.9384891749509083E-2</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.9795964992129699E-2</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.973237885864672E-2</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.9668060396978495E-2</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.9525655931698265E-2</v>
       </c>
       <c r="AC28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.9380431576016434E-2</v>
       </c>
       <c r="AD28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.9232331490519146E-2</v>
       </c>
       <c r="AE28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.9081298730061523E-2</v>
       </c>
       <c r="AF28" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.8927275221872016E-2</v>
       </c>
       <c r="AH28" s="1" t="s">
@@ -4052,7 +4073,7 @@
       </c>
       <c r="AI29" s="5">
         <f>Main!D3</f>
-        <v>180.62</v>
+        <v>195.58</v>
       </c>
     </row>
     <row r="30" spans="2:143" x14ac:dyDescent="0.3">
@@ -4061,7 +4082,7 @@
       </c>
       <c r="AI30" s="11">
         <f>AI28/AI29-1</f>
-        <v>-0.15132262827852416</v>
+        <v>-0.21623833275215787</v>
       </c>
     </row>
     <row r="31" spans="2:143" x14ac:dyDescent="0.3">
@@ -4070,6 +4091,33 @@
       </c>
       <c r="AI31" s="7" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="2:143" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="12">
+        <f>13549</f>
+        <v>13549</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L34" s="13">
+        <f>Main!D9/Model!L32</f>
+        <v>2.1600792678426455</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="10">
+        <f>L32/Main!D9-1</f>
+        <v>-0.53705402626324061</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/LDOS.xlsx
+++ b/Financial Analysis/LDOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07593CC-4F62-4C71-B08E-9E5F6108365D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225CD275-8FCF-402F-A101-2256FC154E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0C5083B5-BD04-437F-9545-422299EC636F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{0C5083B5-BD04-437F-9545-422299EC636F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="70">
   <si>
     <t>LDOS</t>
   </si>
@@ -227,7 +227,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color theme="0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -237,7 +237,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color theme="0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -253,7 +253,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color theme="0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -263,7 +263,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color theme="0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -274,7 +274,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color theme="0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -284,7 +284,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color theme="0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -295,7 +295,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color theme="0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -305,13 +305,25 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color theme="0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -322,7 +334,7 @@
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,14 +380,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -391,7 +395,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -414,11 +418,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -449,6 +490,9 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,14 +514,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:to>
@@ -494,8 +538,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8763000" y="15240"/>
-          <a:ext cx="0" cy="6598920"/>
+          <a:off x="9364980" y="15240"/>
+          <a:ext cx="0" cy="7696200"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -520,13 +564,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
@@ -895,17 +939,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>190.36</v>
+        <v>172.3</v>
       </c>
       <c r="E3" s="4">
-        <v>45988</v>
+        <v>46070</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45988</v>
+        <v>46072</v>
       </c>
       <c r="G3" s="4">
-        <v>46070</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -913,11 +957,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
+        <v>127</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -926,7 +969,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>24347.044000000002</v>
+        <v>21882.100000000002</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -934,11 +977,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>974</f>
-        <v>974</v>
+        <f>1108</f>
+        <v>1108</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -946,13 +989,13 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>19+4632</f>
-        <v>4651</v>
+        <f>20+4628</f>
+        <v>4648</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="18" t="s">
         <v>64</v>
       </c>
     </row>
@@ -962,9 +1005,9 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>-3677</v>
-      </c>
-      <c r="K8"/>
+        <v>-3540</v>
+      </c>
+      <c r="K8" s="19"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="s">
@@ -972,9 +1015,9 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>28024.044000000002</v>
-      </c>
-      <c r="K9" t="s">
+        <v>25422.100000000002</v>
+      </c>
+      <c r="K9" s="20" t="s">
         <v>65</v>
       </c>
     </row>
@@ -985,18 +1028,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D44293-D96C-4AE6-8EBE-24AD359410D0}">
-  <dimension ref="B2:EM45"/>
+  <dimension ref="B2:EQ45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="33" width="8.88671875" style="1"/>
-    <col min="34" max="34" width="13.109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="16.5546875" style="1" customWidth="1"/>
-    <col min="36" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="37" width="8.88671875" style="1"/>
+    <col min="38" max="38" width="13.109375" style="1" customWidth="1"/>
+    <col min="39" max="39" width="16.5546875" style="1" customWidth="1"/>
+    <col min="40" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:36" x14ac:dyDescent="0.3">
       <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
@@ -1033,59 +1076,71 @@
       <c r="N2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="1">
+      <c r="O2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="T2" s="1">
         <v>2019</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="U2" s="1">
         <v>2020</v>
       </c>
-      <c r="R2" s="1">
+      <c r="V2" s="1">
         <v>2021</v>
       </c>
-      <c r="S2" s="1">
+      <c r="W2" s="1">
         <v>2022</v>
       </c>
-      <c r="T2" s="1">
+      <c r="X2" s="1">
         <v>2023</v>
       </c>
-      <c r="U2" s="1">
+      <c r="Y2" s="1">
         <v>2024</v>
       </c>
-      <c r="V2" s="1">
+      <c r="Z2" s="1">
         <v>2025</v>
       </c>
-      <c r="W2" s="1">
+      <c r="AA2" s="1">
         <v>2026</v>
       </c>
-      <c r="X2" s="1">
+      <c r="AB2" s="1">
         <v>2027</v>
       </c>
-      <c r="Y2" s="1">
+      <c r="AC2" s="1">
         <v>2028</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="AD2" s="1">
         <v>2029</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AE2" s="1">
         <v>2030</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AF2" s="1">
         <v>2031</v>
       </c>
-      <c r="AC2" s="1">
+      <c r="AG2" s="1">
         <v>2032</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AH2" s="1">
         <v>2033</v>
       </c>
-      <c r="AE2" s="1">
+      <c r="AI2" s="1">
         <v>2034</v>
       </c>
-      <c r="AF2" s="1">
+      <c r="AJ2" s="1">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>59</v>
       </c>
@@ -1104,12 +1159,18 @@
       <c r="M3" s="15">
         <v>3203</v>
       </c>
-      <c r="N3" s="7"/>
-      <c r="V3" s="15">
-        <v>3203</v>
-      </c>
-    </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="N3" s="15">
+        <v>2749</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="Z3" s="15">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="4" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>60</v>
       </c>
@@ -1128,12 +1189,18 @@
       <c r="M4" s="15">
         <v>1866</v>
       </c>
-      <c r="N4" s="7"/>
-      <c r="V4" s="15">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="N4" s="15">
+        <v>2745</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="Z4" s="15">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="5" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>61</v>
       </c>
@@ -1152,12 +1219,18 @@
       <c r="M5" s="15">
         <v>2549</v>
       </c>
-      <c r="N5" s="7"/>
-      <c r="V5" s="15">
-        <v>2549</v>
-      </c>
-    </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="N5" s="15">
+        <v>2588</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="Z5" s="15">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="6" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>62</v>
       </c>
@@ -1176,12 +1249,18 @@
       <c r="M6" s="15">
         <v>1446</v>
       </c>
-      <c r="N6" s="7"/>
-      <c r="V6" s="15">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="7" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="15">
+        <v>1603</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="Z6" s="15">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="7" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>63</v>
       </c>
@@ -1202,13 +1281,20 @@
         <f>SUM(M3:M6)</f>
         <v>9064</v>
       </c>
-      <c r="N7" s="16"/>
-      <c r="V7" s="17">
-        <f>SUM(V3:V6)</f>
-        <v>9064</v>
-      </c>
-    </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="N7" s="17">
+        <f>SUM(N3:N6)</f>
+        <v>9685</v>
+      </c>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="Z7" s="17">
+        <f>SUM(Z3:Z6)</f>
+        <v>9685</v>
+      </c>
+    </row>
+    <row r="8" spans="2:36" x14ac:dyDescent="0.3">
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
@@ -1221,8 +1307,12 @@
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
-    </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+    </row>
+    <row r="9" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>59</v>
       </c>
@@ -1235,15 +1325,23 @@
       <c r="I9" s="15">
         <v>1865</v>
       </c>
-      <c r="J9" s="7"/>
+      <c r="J9" s="15">
+        <v>1894</v>
+      </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
       <c r="M9" s="15">
         <v>2015</v>
       </c>
-      <c r="N9" s="7"/>
-    </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="N9" s="15">
+        <v>1846</v>
+      </c>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+    </row>
+    <row r="10" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>60</v>
       </c>
@@ -1256,15 +1354,23 @@
       <c r="I10" s="15">
         <v>1225</v>
       </c>
-      <c r="J10" s="7"/>
+      <c r="J10" s="15">
+        <v>1328</v>
+      </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="15">
         <v>1301</v>
       </c>
-      <c r="N10" s="7"/>
-    </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="N10" s="15">
+        <v>1205</v>
+      </c>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+    </row>
+    <row r="11" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>61</v>
       </c>
@@ -1277,15 +1383,23 @@
       <c r="I11" s="15">
         <v>578</v>
       </c>
-      <c r="J11" s="7"/>
+      <c r="J11" s="15">
+        <v>604</v>
+      </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="15">
         <v>571</v>
       </c>
-      <c r="N11" s="7"/>
-    </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="N11" s="15">
+        <v>610</v>
+      </c>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+    </row>
+    <row r="12" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>62</v>
       </c>
@@ -1298,15 +1412,23 @@
       <c r="I12" s="15">
         <v>522</v>
       </c>
-      <c r="J12" s="7"/>
+      <c r="J12" s="15">
+        <v>539</v>
+      </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="15">
         <v>582</v>
       </c>
-      <c r="N12" s="7"/>
-    </row>
-    <row r="13" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N12" s="15">
+        <v>546</v>
+      </c>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+    </row>
+    <row r="13" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1327,7 +1449,7 @@
         <v>4190</v>
       </c>
       <c r="J13" s="9">
-        <f>U13-I13-H13-G13</f>
+        <f>SUM(J9:J12)</f>
         <v>4365</v>
       </c>
       <c r="K13" s="9">
@@ -1340,73 +1462,77 @@
         <v>4469</v>
       </c>
       <c r="N13" s="9">
-        <f t="shared" ref="N13" si="0">J13*1.07</f>
-        <v>4670.55</v>
-      </c>
-      <c r="P13" s="9">
+        <f>SUM(N9:N12)</f>
+        <v>4207</v>
+      </c>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="T13" s="9">
         <v>11094</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="U13" s="9">
         <v>12297</v>
       </c>
-      <c r="R13" s="9">
+      <c r="V13" s="9">
         <v>13737</v>
       </c>
-      <c r="S13" s="9">
+      <c r="W13" s="9">
         <v>14396</v>
       </c>
-      <c r="T13" s="9">
+      <c r="X13" s="9">
         <v>15438</v>
       </c>
-      <c r="U13" s="9">
+      <c r="Y13" s="9">
         <v>16662</v>
       </c>
-      <c r="V13" s="9">
+      <c r="Z13" s="9">
         <f>SUM(K13:N13)</f>
-        <v>17637.55</v>
-      </c>
-      <c r="W13" s="9">
-        <f>V13*1.05</f>
-        <v>18519.427500000002</v>
-      </c>
-      <c r="X13" s="9">
-        <f>W13*1.04</f>
-        <v>19260.204600000001</v>
-      </c>
-      <c r="Y13" s="9">
-        <f>X13*1.03</f>
-        <v>19838.010738000001</v>
-      </c>
-      <c r="Z13" s="9">
-        <f>Y13*1.02</f>
-        <v>20234.770952760002</v>
+        <v>17174</v>
       </c>
       <c r="AA13" s="9">
-        <f>Z13*1.02</f>
-        <v>20639.466371815201</v>
+        <f>Z13*1.03</f>
+        <v>17689.22</v>
       </c>
       <c r="AB13" s="9">
-        <f>AA13*1.01</f>
-        <v>20845.861035533351</v>
+        <f>AA13*1.03</f>
+        <v>18219.8966</v>
       </c>
       <c r="AC13" s="9">
-        <f t="shared" ref="AC13:AF13" si="1">AB13*1.01</f>
-        <v>21054.319645888685</v>
+        <f>AB13*1.03</f>
+        <v>18766.493498</v>
       </c>
       <c r="AD13" s="9">
-        <f t="shared" si="1"/>
-        <v>21264.862842347571</v>
+        <f>AC13*1.02</f>
+        <v>19141.823367960002</v>
       </c>
       <c r="AE13" s="9">
-        <f t="shared" si="1"/>
-        <v>21477.511470771045</v>
+        <f>AD13*1.02</f>
+        <v>19524.659835319202</v>
       </c>
       <c r="AF13" s="9">
-        <f t="shared" si="1"/>
-        <v>21692.286585478756</v>
-      </c>
-    </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.3">
+        <f>AE13*1.01</f>
+        <v>19719.906433672393</v>
+      </c>
+      <c r="AG13" s="9">
+        <f t="shared" ref="AG13:AJ13" si="0">AF13*1.01</f>
+        <v>19917.105498009118</v>
+      </c>
+      <c r="AH13" s="9">
+        <f t="shared" si="0"/>
+        <v>20116.276552989209</v>
+      </c>
+      <c r="AI13" s="9">
+        <f t="shared" si="0"/>
+        <v>20317.4393185191</v>
+      </c>
+      <c r="AJ13" s="9">
+        <f t="shared" si="0"/>
+        <v>20520.613711704293</v>
+      </c>
+    </row>
+    <row r="14" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
@@ -1426,7 +1552,7 @@
         <v>3428</v>
       </c>
       <c r="J14" s="6">
-        <f>U14-I14-H14-G14</f>
+        <f>Y14-I14-H14-G14</f>
         <v>3672</v>
       </c>
       <c r="K14" s="6">
@@ -1439,73 +1565,76 @@
         <v>3648</v>
       </c>
       <c r="N14" s="6">
-        <f t="shared" ref="N14" si="2">N13-N15</f>
-        <v>3876.5565000000001</v>
-      </c>
-      <c r="P14" s="6">
+        <v>3468</v>
+      </c>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="T14" s="6">
         <v>9546</v>
       </c>
-      <c r="Q14" s="6">
+      <c r="U14" s="6">
         <v>10560</v>
       </c>
-      <c r="R14" s="6">
+      <c r="V14" s="6">
         <v>11723</v>
       </c>
-      <c r="S14" s="6">
+      <c r="W14" s="6">
         <v>12312</v>
       </c>
-      <c r="T14" s="6">
+      <c r="X14" s="6">
         <v>13194</v>
       </c>
-      <c r="U14" s="6">
+      <c r="Y14" s="6">
         <v>13864</v>
       </c>
-      <c r="V14" s="6">
+      <c r="Z14" s="6">
         <f>SUM(K14:N14)</f>
-        <v>14483.556500000001</v>
-      </c>
-      <c r="W14" s="6">
-        <f>W13-W15</f>
-        <v>15185.930550000001</v>
-      </c>
-      <c r="X14" s="6">
-        <f t="shared" ref="X14:AF14" si="3">X13-X15</f>
-        <v>15793.367772000001</v>
-      </c>
-      <c r="Y14" s="6">
-        <f t="shared" si="3"/>
-        <v>16267.168805160001</v>
-      </c>
-      <c r="Z14" s="6">
-        <f t="shared" si="3"/>
-        <v>16592.512181263202</v>
+        <v>14075</v>
       </c>
       <c r="AA14" s="6">
-        <f t="shared" si="3"/>
-        <v>16924.362424888466</v>
+        <f>AA13-AA15</f>
+        <v>14505.160400000001</v>
       </c>
       <c r="AB14" s="6">
-        <f t="shared" si="3"/>
-        <v>17093.60604913735</v>
+        <f t="shared" ref="AB14:AJ14" si="1">AB13-AB15</f>
+        <v>14940.315212</v>
       </c>
       <c r="AC14" s="6">
-        <f t="shared" si="3"/>
-        <v>17264.542109628721</v>
+        <f t="shared" si="1"/>
+        <v>15388.52466836</v>
       </c>
       <c r="AD14" s="6">
-        <f t="shared" si="3"/>
-        <v>17437.187530725008</v>
+        <f t="shared" si="1"/>
+        <v>15696.295161727201</v>
       </c>
       <c r="AE14" s="6">
-        <f t="shared" si="3"/>
-        <v>17611.559406032258</v>
+        <f t="shared" si="1"/>
+        <v>16010.221064961746</v>
       </c>
       <c r="AF14" s="6">
-        <f t="shared" si="3"/>
-        <v>17787.675000092579</v>
-      </c>
-    </row>
-    <row r="15" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>16170.323275611363</v>
+      </c>
+      <c r="AG14" s="6">
+        <f t="shared" si="1"/>
+        <v>16332.026508367477</v>
+      </c>
+      <c r="AH14" s="6">
+        <f t="shared" si="1"/>
+        <v>16495.346773451151</v>
+      </c>
+      <c r="AI14" s="6">
+        <f t="shared" si="1"/>
+        <v>16660.300241185661</v>
+      </c>
+      <c r="AJ14" s="6">
+        <f t="shared" si="1"/>
+        <v>16826.90324359752</v>
+      </c>
+    </row>
+    <row r="15" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
@@ -1518,107 +1647,111 @@
         <v>587</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" ref="G15:M15" si="4">G13-G14</f>
+        <f t="shared" ref="G15:N15" si="2">G13-G14</f>
         <v>638</v>
       </c>
       <c r="H15" s="9">
+        <f t="shared" si="2"/>
+        <v>705</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="2"/>
+        <v>762</v>
+      </c>
+      <c r="J15" s="9">
+        <f t="shared" si="2"/>
+        <v>693</v>
+      </c>
+      <c r="K15" s="9">
+        <f t="shared" si="2"/>
+        <v>757</v>
+      </c>
+      <c r="L15" s="9">
+        <f t="shared" si="2"/>
+        <v>782</v>
+      </c>
+      <c r="M15" s="9">
+        <f t="shared" si="2"/>
+        <v>821</v>
+      </c>
+      <c r="N15" s="9">
+        <f t="shared" si="2"/>
+        <v>739</v>
+      </c>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="T15" s="9">
+        <f t="shared" ref="T15:Z15" si="3">T13-T14</f>
+        <v>1548</v>
+      </c>
+      <c r="U15" s="9">
+        <f t="shared" si="3"/>
+        <v>1737</v>
+      </c>
+      <c r="V15" s="9">
+        <f t="shared" si="3"/>
+        <v>2014</v>
+      </c>
+      <c r="W15" s="9">
+        <f t="shared" si="3"/>
+        <v>2084</v>
+      </c>
+      <c r="X15" s="9">
+        <f t="shared" si="3"/>
+        <v>2244</v>
+      </c>
+      <c r="Y15" s="9">
+        <f t="shared" si="3"/>
+        <v>2798</v>
+      </c>
+      <c r="Z15" s="9">
+        <f t="shared" si="3"/>
+        <v>3099</v>
+      </c>
+      <c r="AA15" s="9">
+        <f>AA13*0.18</f>
+        <v>3184.0596</v>
+      </c>
+      <c r="AB15" s="9">
+        <f t="shared" ref="AB15:AJ15" si="4">AB13*0.18</f>
+        <v>3279.5813880000001</v>
+      </c>
+      <c r="AC15" s="9">
         <f t="shared" si="4"/>
-        <v>705</v>
-      </c>
-      <c r="I15" s="9">
+        <v>3377.96882964</v>
+      </c>
+      <c r="AD15" s="9">
         <f t="shared" si="4"/>
-        <v>762</v>
-      </c>
-      <c r="J15" s="9">
+        <v>3445.5282062328001</v>
+      </c>
+      <c r="AE15" s="9">
         <f t="shared" si="4"/>
-        <v>693</v>
-      </c>
-      <c r="K15" s="9">
+        <v>3514.4387703574562</v>
+      </c>
+      <c r="AF15" s="9">
         <f t="shared" si="4"/>
-        <v>757</v>
-      </c>
-      <c r="L15" s="9">
+        <v>3549.5831580610306</v>
+      </c>
+      <c r="AG15" s="9">
         <f t="shared" si="4"/>
-        <v>782</v>
-      </c>
-      <c r="M15" s="9">
+        <v>3585.0789896416409</v>
+      </c>
+      <c r="AH15" s="9">
         <f t="shared" si="4"/>
-        <v>821</v>
-      </c>
-      <c r="N15" s="9">
-        <f t="shared" ref="N15" si="5">N13*0.17</f>
-        <v>793.99350000000004</v>
-      </c>
-      <c r="P15" s="9">
-        <f t="shared" ref="P15:V15" si="6">P13-P14</f>
-        <v>1548</v>
-      </c>
-      <c r="Q15" s="9">
-        <f t="shared" si="6"/>
-        <v>1737</v>
-      </c>
-      <c r="R15" s="9">
-        <f t="shared" si="6"/>
-        <v>2014</v>
-      </c>
-      <c r="S15" s="9">
-        <f t="shared" si="6"/>
-        <v>2084</v>
-      </c>
-      <c r="T15" s="9">
-        <f t="shared" si="6"/>
-        <v>2244</v>
-      </c>
-      <c r="U15" s="9">
-        <f t="shared" si="6"/>
-        <v>2798</v>
-      </c>
-      <c r="V15" s="9">
-        <f t="shared" si="6"/>
-        <v>3153.9934999999987</v>
-      </c>
-      <c r="W15" s="9">
-        <f>W13*0.18</f>
-        <v>3333.4969500000002</v>
-      </c>
-      <c r="X15" s="9">
-        <f t="shared" ref="X15:AF15" si="7">X13*0.18</f>
-        <v>3466.836828</v>
-      </c>
-      <c r="Y15" s="9">
-        <f t="shared" si="7"/>
-        <v>3570.84193284</v>
-      </c>
-      <c r="Z15" s="9">
-        <f t="shared" si="7"/>
-        <v>3642.2587714968004</v>
-      </c>
-      <c r="AA15" s="9">
-        <f t="shared" si="7"/>
-        <v>3715.1039469267362</v>
-      </c>
-      <c r="AB15" s="9">
-        <f t="shared" si="7"/>
-        <v>3752.254986396003</v>
-      </c>
-      <c r="AC15" s="9">
-        <f t="shared" si="7"/>
-        <v>3789.7775362599632</v>
-      </c>
-      <c r="AD15" s="9">
-        <f t="shared" si="7"/>
-        <v>3827.6753116225627</v>
-      </c>
-      <c r="AE15" s="9">
-        <f t="shared" si="7"/>
-        <v>3865.9520647387881</v>
-      </c>
-      <c r="AF15" s="9">
-        <f t="shared" si="7"/>
-        <v>3904.6115853861761</v>
-      </c>
-    </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.3">
+        <v>3620.9297795380576</v>
+      </c>
+      <c r="AI15" s="9">
+        <f t="shared" si="4"/>
+        <v>3657.1390773334379</v>
+      </c>
+      <c r="AJ15" s="9">
+        <f t="shared" si="4"/>
+        <v>3693.7104681067726</v>
+      </c>
+    </row>
+    <row r="16" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>26</v>
       </c>
@@ -1638,7 +1771,7 @@
         <v>247</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" ref="J16:J18" si="8">U16-I16-H16-G16</f>
+        <f t="shared" ref="J16:J18" si="5">Y16-I16-H16-G16</f>
         <v>279</v>
       </c>
       <c r="K16" s="6">
@@ -1651,76 +1784,79 @@
         <v>286</v>
       </c>
       <c r="N16" s="6">
-        <f>J16*1.01</f>
-        <v>281.79000000000002</v>
-      </c>
-      <c r="P16" s="6">
+        <v>266</v>
+      </c>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="T16" s="6">
         <f>689-40</f>
         <v>649</v>
       </c>
-      <c r="Q16" s="6">
+      <c r="U16" s="6">
         <f>770-68</f>
         <v>702</v>
       </c>
-      <c r="R16" s="6">
+      <c r="V16" s="6">
         <f>860-9</f>
         <v>851</v>
       </c>
-      <c r="S16" s="6">
+      <c r="W16" s="6">
         <v>951</v>
       </c>
-      <c r="T16" s="6">
+      <c r="X16" s="6">
         <v>942</v>
       </c>
-      <c r="U16" s="6">
+      <c r="Y16" s="6">
         <v>983</v>
       </c>
-      <c r="V16" s="6">
-        <f t="shared" ref="V16:V18" si="9">SUM(K16:N16)</f>
-        <v>1014.79</v>
-      </c>
-      <c r="W16" s="6">
-        <f>V16*1.02</f>
-        <v>1035.0858000000001</v>
-      </c>
-      <c r="X16" s="6">
-        <f t="shared" ref="X16:AA16" si="10">W16*1.02</f>
-        <v>1055.7875160000001</v>
-      </c>
-      <c r="Y16" s="6">
-        <f t="shared" si="10"/>
-        <v>1076.9032663200001</v>
-      </c>
       <c r="Z16" s="6">
-        <f t="shared" si="10"/>
-        <v>1098.4413316464002</v>
+        <f t="shared" ref="Z16:Z18" si="6">SUM(K16:N16)</f>
+        <v>999</v>
       </c>
       <c r="AA16" s="6">
-        <f t="shared" si="10"/>
-        <v>1120.4101582793282</v>
+        <f>Z16*1.02</f>
+        <v>1018.98</v>
       </c>
       <c r="AB16" s="6">
-        <f>AA16*1.01</f>
-        <v>1131.6142598621216</v>
+        <f t="shared" ref="AB16:AE16" si="7">AA16*1.02</f>
+        <v>1039.3596</v>
       </c>
       <c r="AC16" s="6">
-        <f t="shared" ref="AC16:AF16" si="11">AB16*1.01</f>
-        <v>1142.9304024607427</v>
+        <f t="shared" si="7"/>
+        <v>1060.146792</v>
       </c>
       <c r="AD16" s="6">
-        <f t="shared" si="11"/>
-        <v>1154.3597064853502</v>
+        <f t="shared" si="7"/>
+        <v>1081.34972784</v>
       </c>
       <c r="AE16" s="6">
-        <f t="shared" si="11"/>
-        <v>1165.9033035502036</v>
+        <f t="shared" si="7"/>
+        <v>1102.9767223968001</v>
       </c>
       <c r="AF16" s="6">
-        <f t="shared" si="11"/>
-        <v>1177.5623365857057</v>
-      </c>
-    </row>
-    <row r="17" spans="2:143" x14ac:dyDescent="0.3">
+        <f>AE16*1.01</f>
+        <v>1114.0064896207682</v>
+      </c>
+      <c r="AG16" s="6">
+        <f t="shared" ref="AG16:AJ16" si="8">AF16*1.01</f>
+        <v>1125.1465545169758</v>
+      </c>
+      <c r="AH16" s="6">
+        <f t="shared" si="8"/>
+        <v>1136.3980200621456</v>
+      </c>
+      <c r="AI16" s="6">
+        <f t="shared" si="8"/>
+        <v>1147.7620002627671</v>
+      </c>
+      <c r="AJ16" s="6">
+        <f t="shared" si="8"/>
+        <v>1159.2396202653947</v>
+      </c>
+    </row>
+    <row r="17" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1740,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="K17" s="6">
@@ -1753,72 +1889,76 @@
         <v>4</v>
       </c>
       <c r="N17" s="6">
-        <v>4</v>
-      </c>
-      <c r="P17" s="6">
+        <v>8</v>
+      </c>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="T17" s="6">
         <v>5</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="U17" s="6">
         <v>39</v>
       </c>
-      <c r="R17" s="6">
+      <c r="V17" s="6">
         <v>27</v>
       </c>
-      <c r="S17" s="6">
+      <c r="W17" s="6">
         <v>17</v>
       </c>
-      <c r="T17" s="6">
+      <c r="X17" s="6">
         <v>24</v>
       </c>
-      <c r="U17" s="6">
+      <c r="Y17" s="6">
         <v>16</v>
       </c>
-      <c r="V17" s="6">
+      <c r="Z17" s="6">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="AA17" s="6">
+        <f>Z17*1.01</f>
+        <v>18.18</v>
+      </c>
+      <c r="AB17" s="6">
+        <f t="shared" ref="AB17:AJ17" si="9">AA17*1.01</f>
+        <v>18.361799999999999</v>
+      </c>
+      <c r="AC17" s="6">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="W17" s="6">
-        <f>V17*1.01</f>
-        <v>14.14</v>
-      </c>
-      <c r="X17" s="6">
-        <f t="shared" ref="X17:AF17" si="12">W17*1.01</f>
-        <v>14.281400000000001</v>
-      </c>
-      <c r="Y17" s="6">
-        <f t="shared" si="12"/>
-        <v>14.424214000000001</v>
-      </c>
-      <c r="Z17" s="6">
-        <f t="shared" si="12"/>
-        <v>14.56845614</v>
-      </c>
-      <c r="AA17" s="6">
-        <f t="shared" si="12"/>
-        <v>14.7141407014</v>
-      </c>
-      <c r="AB17" s="6">
-        <f t="shared" si="12"/>
-        <v>14.861282108414001</v>
-      </c>
-      <c r="AC17" s="6">
-        <f t="shared" si="12"/>
-        <v>15.00989492949814</v>
+        <v>18.545417999999998</v>
       </c>
       <c r="AD17" s="6">
-        <f t="shared" si="12"/>
-        <v>15.159993878793122</v>
+        <f t="shared" si="9"/>
+        <v>18.730872179999999</v>
       </c>
       <c r="AE17" s="6">
-        <f t="shared" si="12"/>
-        <v>15.311593817581054</v>
+        <f t="shared" si="9"/>
+        <v>18.9181809018</v>
       </c>
       <c r="AF17" s="6">
-        <f t="shared" si="12"/>
-        <v>15.464709755756864</v>
-      </c>
-    </row>
-    <row r="18" spans="2:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v>19.107362710817998</v>
+      </c>
+      <c r="AG17" s="6">
+        <f t="shared" si="9"/>
+        <v>19.29843633792618</v>
+      </c>
+      <c r="AH17" s="6">
+        <f t="shared" si="9"/>
+        <v>19.491420701305444</v>
+      </c>
+      <c r="AI17" s="6">
+        <f t="shared" si="9"/>
+        <v>19.6863349083185</v>
+      </c>
+      <c r="AJ17" s="6">
+        <f t="shared" si="9"/>
+        <v>19.883198257401684</v>
+      </c>
+    </row>
+    <row r="18" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>39</v>
       </c>
@@ -1837,7 +1977,7 @@
         <v>6</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="K18" s="6"/>
@@ -1848,42 +1988,34 @@
         <v>4</v>
       </c>
       <c r="N18" s="6">
+        <v>1</v>
+      </c>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="P18" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6">
+      <c r="U18" s="6">
         <v>12</v>
       </c>
-      <c r="R18" s="6">
+      <c r="V18" s="6">
         <v>4</v>
       </c>
-      <c r="S18" s="6">
+      <c r="W18" s="6">
         <v>40</v>
       </c>
-      <c r="T18" s="6">
+      <c r="X18" s="6">
         <f>596+91</f>
         <v>687</v>
       </c>
-      <c r="U18" s="6">
+      <c r="Y18" s="6">
         <v>11</v>
       </c>
-      <c r="V18" s="6">
-        <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="W18" s="6">
-        <v>0</v>
-      </c>
-      <c r="X18" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="6">
-        <v>0</v>
-      </c>
       <c r="Z18" s="6">
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="AA18" s="6">
         <v>0</v>
@@ -1903,8 +2035,20 @@
       <c r="AF18" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:143" x14ac:dyDescent="0.3">
+      <c r="AG18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>38</v>
       </c>
@@ -1937,87 +2081,91 @@
         <v>234</v>
       </c>
       <c r="L19" s="6">
-        <f t="shared" ref="L19:N19" si="13">SUM(L16:L18)</f>
+        <f t="shared" ref="L19:N19" si="10">SUM(L16:L18)</f>
         <v>219</v>
       </c>
       <c r="M19" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>294</v>
       </c>
       <c r="N19" s="6">
-        <f t="shared" si="13"/>
-        <v>285.79000000000002</v>
-      </c>
-      <c r="P19" s="6">
-        <f t="shared" ref="P19:W19" si="14">SUM(P16:P18)</f>
+        <f t="shared" si="10"/>
+        <v>275</v>
+      </c>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="T19" s="6">
+        <f t="shared" ref="T19:AA19" si="11">SUM(T16:T18)</f>
         <v>654</v>
       </c>
-      <c r="Q19" s="6">
-        <f t="shared" si="14"/>
+      <c r="U19" s="6">
+        <f t="shared" si="11"/>
         <v>753</v>
       </c>
-      <c r="R19" s="6">
-        <f t="shared" si="14"/>
+      <c r="V19" s="6">
+        <f t="shared" si="11"/>
         <v>882</v>
       </c>
-      <c r="S19" s="6">
-        <f t="shared" si="14"/>
+      <c r="W19" s="6">
+        <f t="shared" si="11"/>
         <v>1008</v>
       </c>
-      <c r="T19" s="6">
-        <f t="shared" si="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="11"/>
         <v>1653</v>
       </c>
-      <c r="U19" s="6">
-        <f t="shared" si="14"/>
+      <c r="Y19" s="6">
+        <f t="shared" si="11"/>
         <v>1010</v>
       </c>
-      <c r="V19" s="6">
-        <f t="shared" si="14"/>
-        <v>1032.79</v>
-      </c>
-      <c r="W19" s="6">
-        <f t="shared" si="14"/>
-        <v>1049.2258000000002</v>
-      </c>
-      <c r="X19" s="6">
-        <f t="shared" ref="X19:AF19" si="15">SUM(X16:X18)</f>
-        <v>1070.0689160000002</v>
-      </c>
-      <c r="Y19" s="6">
-        <f t="shared" si="15"/>
-        <v>1091.3274803199999</v>
-      </c>
       <c r="Z19" s="6">
-        <f t="shared" si="15"/>
-        <v>1113.0097877864002</v>
+        <f t="shared" si="11"/>
+        <v>1022</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" si="15"/>
-        <v>1135.1242989807283</v>
+        <f t="shared" si="11"/>
+        <v>1037.1600000000001</v>
       </c>
       <c r="AB19" s="6">
-        <f t="shared" si="15"/>
-        <v>1146.4755419705355</v>
+        <f t="shared" ref="AB19:AJ19" si="12">SUM(AB16:AB18)</f>
+        <v>1057.7213999999999</v>
       </c>
       <c r="AC19" s="6">
-        <f t="shared" si="15"/>
-        <v>1157.9402973902409</v>
+        <f t="shared" si="12"/>
+        <v>1078.6922099999999</v>
       </c>
       <c r="AD19" s="6">
-        <f t="shared" si="15"/>
-        <v>1169.5197003641433</v>
+        <f t="shared" si="12"/>
+        <v>1100.08060002</v>
       </c>
       <c r="AE19" s="6">
-        <f t="shared" si="15"/>
-        <v>1181.2148973677847</v>
+        <f t="shared" si="12"/>
+        <v>1121.8949032986002</v>
       </c>
       <c r="AF19" s="6">
-        <f t="shared" si="15"/>
-        <v>1193.0270463414624</v>
-      </c>
-    </row>
-    <row r="20" spans="2:143" s="2" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="12"/>
+        <v>1133.1138523315863</v>
+      </c>
+      <c r="AG19" s="6">
+        <f t="shared" si="12"/>
+        <v>1144.444990854902</v>
+      </c>
+      <c r="AH19" s="6">
+        <f t="shared" si="12"/>
+        <v>1155.8894407634511</v>
+      </c>
+      <c r="AI19" s="6">
+        <f t="shared" si="12"/>
+        <v>1167.4483351710855</v>
+      </c>
+      <c r="AJ19" s="6">
+        <f t="shared" si="12"/>
+        <v>1179.1228185227965</v>
+      </c>
+    </row>
+    <row r="20" spans="2:147" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
@@ -2050,87 +2198,91 @@
         <v>523</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" ref="L20:N20" si="16">L15-L19</f>
+        <f t="shared" ref="L20:N20" si="13">L15-L19</f>
         <v>563</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>527</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="16"/>
-        <v>508.20350000000002</v>
-      </c>
-      <c r="P20" s="9">
-        <f t="shared" ref="P20:W20" si="17">P15-P19</f>
+        <f t="shared" si="13"/>
+        <v>464</v>
+      </c>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="T20" s="9">
+        <f t="shared" ref="T20:AA20" si="14">T15-T19</f>
         <v>894</v>
       </c>
-      <c r="Q20" s="9">
-        <f t="shared" si="17"/>
+      <c r="U20" s="9">
+        <f t="shared" si="14"/>
         <v>984</v>
       </c>
-      <c r="R20" s="9">
-        <f t="shared" si="17"/>
+      <c r="V20" s="9">
+        <f t="shared" si="14"/>
         <v>1132</v>
       </c>
-      <c r="S20" s="9">
-        <f t="shared" si="17"/>
+      <c r="W20" s="9">
+        <f t="shared" si="14"/>
         <v>1076</v>
       </c>
-      <c r="T20" s="9">
-        <f t="shared" si="17"/>
+      <c r="X20" s="9">
+        <f t="shared" si="14"/>
         <v>591</v>
       </c>
-      <c r="U20" s="9">
-        <f t="shared" si="17"/>
+      <c r="Y20" s="9">
+        <f t="shared" si="14"/>
         <v>1788</v>
       </c>
-      <c r="V20" s="9">
-        <f t="shared" si="17"/>
-        <v>2121.2034999999987</v>
-      </c>
-      <c r="W20" s="9">
-        <f t="shared" si="17"/>
-        <v>2284.27115</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" ref="X20:AF20" si="18">X15-X19</f>
-        <v>2396.7679119999998</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" si="18"/>
-        <v>2479.5144525200003</v>
-      </c>
       <c r="Z20" s="9">
-        <f t="shared" si="18"/>
-        <v>2529.2489837104004</v>
+        <f t="shared" si="14"/>
+        <v>2077</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" si="18"/>
-        <v>2579.9796479460078</v>
+        <f t="shared" si="14"/>
+        <v>2146.8995999999997</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" si="18"/>
-        <v>2605.7794444254678</v>
+        <f t="shared" ref="AB20:AJ20" si="15">AB15-AB19</f>
+        <v>2221.8599880000002</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" si="18"/>
-        <v>2631.8372388697226</v>
+        <f t="shared" si="15"/>
+        <v>2299.2766196399998</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" si="18"/>
-        <v>2658.1556112584194</v>
+        <f t="shared" si="15"/>
+        <v>2345.4476062128001</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="18"/>
-        <v>2684.7371673710031</v>
+        <f t="shared" si="15"/>
+        <v>2392.543867058856</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" si="18"/>
-        <v>2711.5845390447139</v>
-      </c>
-    </row>
-    <row r="21" spans="2:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="15"/>
+        <v>2416.4693057294444</v>
+      </c>
+      <c r="AG20" s="9">
+        <f t="shared" si="15"/>
+        <v>2440.6339987867386</v>
+      </c>
+      <c r="AH20" s="9">
+        <f t="shared" si="15"/>
+        <v>2465.0403387746064</v>
+      </c>
+      <c r="AI20" s="9">
+        <f t="shared" si="15"/>
+        <v>2489.6907421623523</v>
+      </c>
+      <c r="AJ20" s="9">
+        <f t="shared" si="15"/>
+        <v>2514.5876495839761</v>
+      </c>
+    </row>
+    <row r="21" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,7 +2302,7 @@
         <v>-10</v>
       </c>
       <c r="J21" s="6">
-        <f t="shared" ref="J21:J22" si="19">U21-I21-H21-G21</f>
+        <f t="shared" ref="J21:J22" si="16">Y21-I21-H21-G21</f>
         <v>-14</v>
       </c>
       <c r="K21" s="6">
@@ -2163,73 +2315,76 @@
         <v>-8</v>
       </c>
       <c r="N21" s="6">
-        <f t="shared" ref="N21" si="20">J21*1.03</f>
-        <v>-14.42</v>
-      </c>
-      <c r="P21" s="6">
+        <v>-9</v>
+      </c>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="T21" s="6">
         <v>-18</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="U21" s="6">
         <v>-14</v>
       </c>
-      <c r="R21" s="6">
+      <c r="V21" s="6">
         <v>-20</v>
       </c>
-      <c r="S21" s="6">
+      <c r="W21" s="6">
         <v>-12</v>
       </c>
-      <c r="T21" s="6">
+      <c r="X21" s="6">
         <v>-30</v>
       </c>
-      <c r="U21" s="6">
+      <c r="Y21" s="6">
         <v>-39</v>
       </c>
-      <c r="V21" s="6">
-        <f t="shared" ref="V21:V23" si="21">SUM(K21:N21)</f>
-        <v>-37.42</v>
-      </c>
-      <c r="W21" s="6">
-        <f>V21*1.03</f>
-        <v>-38.5426</v>
-      </c>
-      <c r="X21" s="6">
-        <f t="shared" ref="X21:AF21" si="22">W21*1.03</f>
-        <v>-39.698878000000001</v>
-      </c>
-      <c r="Y21" s="6">
-        <f t="shared" si="22"/>
-        <v>-40.889844340000003</v>
-      </c>
       <c r="Z21" s="6">
-        <f t="shared" si="22"/>
-        <v>-42.116539670200005</v>
+        <f t="shared" ref="Z21:Z23" si="17">SUM(K21:N21)</f>
+        <v>-32</v>
       </c>
       <c r="AA21" s="6">
-        <f t="shared" si="22"/>
-        <v>-43.380035860306009</v>
+        <f>Z21*1.03</f>
+        <v>-32.96</v>
       </c>
       <c r="AB21" s="6">
-        <f t="shared" si="22"/>
-        <v>-44.68143693611519</v>
+        <f t="shared" ref="AB21:AJ21" si="18">AA21*1.03</f>
+        <v>-33.948799999999999</v>
       </c>
       <c r="AC21" s="6">
-        <f t="shared" si="22"/>
-        <v>-46.021880044198646</v>
+        <f t="shared" si="18"/>
+        <v>-34.967264</v>
       </c>
       <c r="AD21" s="6">
-        <f t="shared" si="22"/>
-        <v>-47.402536445524603</v>
+        <f t="shared" si="18"/>
+        <v>-36.016281920000004</v>
       </c>
       <c r="AE21" s="6">
-        <f t="shared" si="22"/>
-        <v>-48.824612538890342</v>
+        <f t="shared" si="18"/>
+        <v>-37.096770377600002</v>
       </c>
       <c r="AF21" s="6">
-        <f t="shared" si="22"/>
-        <v>-50.289350915057057</v>
-      </c>
-    </row>
-    <row r="22" spans="2:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>-38.209673488928004</v>
+      </c>
+      <c r="AG21" s="6">
+        <f t="shared" si="18"/>
+        <v>-39.355963693595847</v>
+      </c>
+      <c r="AH21" s="6">
+        <f t="shared" si="18"/>
+        <v>-40.536642604403724</v>
+      </c>
+      <c r="AI21" s="6">
+        <f t="shared" si="18"/>
+        <v>-41.752741882535837</v>
+      </c>
+      <c r="AJ21" s="6">
+        <f t="shared" si="18"/>
+        <v>-43.005324139011911</v>
+      </c>
+    </row>
+    <row r="22" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>30</v>
       </c>
@@ -2249,7 +2404,7 @@
         <v>46</v>
       </c>
       <c r="J22" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>47</v>
       </c>
       <c r="K22" s="6">
@@ -2262,72 +2417,76 @@
         <v>51</v>
       </c>
       <c r="N22" s="6">
-        <v>50</v>
-      </c>
-      <c r="P22" s="6">
+        <v>48</v>
+      </c>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="T22" s="6">
         <v>133</v>
       </c>
-      <c r="Q22" s="6">
+      <c r="U22" s="6">
         <v>179</v>
       </c>
-      <c r="R22" s="6">
+      <c r="V22" s="6">
         <v>184</v>
       </c>
-      <c r="S22" s="6">
+      <c r="W22" s="6">
         <v>199</v>
       </c>
-      <c r="T22" s="6">
+      <c r="X22" s="6">
         <v>212</v>
       </c>
-      <c r="U22" s="6">
+      <c r="Y22" s="6">
         <v>193</v>
       </c>
-      <c r="V22" s="6">
-        <f t="shared" si="21"/>
-        <v>205</v>
-      </c>
-      <c r="W22" s="6">
-        <f>V22*1.03</f>
-        <v>211.15</v>
-      </c>
-      <c r="X22" s="6">
-        <f t="shared" ref="X22:AF22" si="23">W22*1.03</f>
-        <v>217.48450000000003</v>
-      </c>
-      <c r="Y22" s="6">
-        <f t="shared" si="23"/>
-        <v>224.00903500000004</v>
-      </c>
       <c r="Z22" s="6">
-        <f t="shared" si="23"/>
-        <v>230.72930605000005</v>
+        <f t="shared" si="17"/>
+        <v>203</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="23"/>
-        <v>237.65118523150005</v>
+        <f>Z22*1.03</f>
+        <v>209.09</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="23"/>
-        <v>244.78072078844505</v>
+        <f t="shared" ref="AB22:AJ22" si="19">AA22*1.03</f>
+        <v>215.36270000000002</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="23"/>
-        <v>252.12414241209842</v>
+        <f t="shared" si="19"/>
+        <v>221.82358100000002</v>
       </c>
       <c r="AD22" s="6">
-        <f t="shared" si="23"/>
-        <v>259.68786668446137</v>
+        <f t="shared" si="19"/>
+        <v>228.47828843000002</v>
       </c>
       <c r="AE22" s="6">
-        <f t="shared" si="23"/>
-        <v>267.47850268499519</v>
+        <f t="shared" si="19"/>
+        <v>235.33263708290002</v>
       </c>
       <c r="AF22" s="6">
-        <f t="shared" si="23"/>
-        <v>275.50285776554506</v>
-      </c>
-    </row>
-    <row r="23" spans="2:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="19"/>
+        <v>242.39261619538703</v>
+      </c>
+      <c r="AG22" s="6">
+        <f t="shared" si="19"/>
+        <v>249.66439468124867</v>
+      </c>
+      <c r="AH22" s="6">
+        <f t="shared" si="19"/>
+        <v>257.15432652168613</v>
+      </c>
+      <c r="AI22" s="6">
+        <f t="shared" si="19"/>
+        <v>264.86895631733671</v>
+      </c>
+      <c r="AJ22" s="6">
+        <f t="shared" si="19"/>
+        <v>272.81502500685684</v>
+      </c>
+    </row>
+    <row r="23" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>31</v>
       </c>
@@ -2347,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="6">
-        <f>U23-I23-H23-G23</f>
+        <f>Y23-I23-H23-G23</f>
         <v>-1</v>
       </c>
       <c r="K23" s="6">
@@ -2360,41 +2519,33 @@
         <v>0</v>
       </c>
       <c r="N23" s="6">
-        <v>0</v>
-      </c>
-      <c r="P23" s="6">
+        <v>-4</v>
+      </c>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="T23" s="6">
         <v>-87</v>
       </c>
-      <c r="Q23" s="6">
+      <c r="U23" s="6">
         <v>38</v>
       </c>
-      <c r="R23" s="6">
+      <c r="V23" s="6">
         <v>1</v>
       </c>
-      <c r="S23" s="6">
+      <c r="W23" s="6">
         <v>3</v>
       </c>
-      <c r="T23" s="6">
+      <c r="X23" s="6">
         <v>6</v>
       </c>
-      <c r="U23" s="6">
+      <c r="Y23" s="6">
         <v>-5</v>
       </c>
-      <c r="V23" s="6">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="W23" s="6">
-        <v>0</v>
-      </c>
-      <c r="X23" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="6">
-        <v>0</v>
-      </c>
       <c r="Z23" s="6">
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>-3</v>
       </c>
       <c r="AA23" s="6">
         <v>0</v>
@@ -2414,8 +2565,20 @@
       <c r="AF23" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:143" x14ac:dyDescent="0.3">
+      <c r="AG23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>32</v>
       </c>
@@ -2428,107 +2591,111 @@
         <v>44</v>
       </c>
       <c r="G24" s="6">
-        <f t="shared" ref="G24:L24" si="24">SUM(G21:G23)</f>
+        <f t="shared" ref="G24:L24" si="20">SUM(G21:G23)</f>
         <v>40</v>
       </c>
       <c r="H24" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>41</v>
       </c>
       <c r="I24" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>36</v>
       </c>
       <c r="J24" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>32</v>
       </c>
       <c r="K24" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>45</v>
       </c>
       <c r="L24" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>45</v>
       </c>
       <c r="M24" s="6">
-        <f t="shared" ref="M24:N24" si="25">SUM(M21:M23)</f>
+        <f t="shared" ref="M24:N24" si="21">SUM(M21:M23)</f>
         <v>43</v>
       </c>
       <c r="N24" s="6">
-        <f t="shared" si="25"/>
-        <v>35.58</v>
-      </c>
-      <c r="P24" s="6">
-        <f t="shared" ref="P24:W24" si="26">SUM(P21:P23)</f>
+        <f t="shared" si="21"/>
+        <v>35</v>
+      </c>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="T24" s="6">
+        <f t="shared" ref="T24:AA24" si="22">SUM(T21:T23)</f>
         <v>28</v>
       </c>
-      <c r="Q24" s="6">
-        <f t="shared" si="26"/>
+      <c r="U24" s="6">
+        <f t="shared" si="22"/>
         <v>203</v>
       </c>
-      <c r="R24" s="6">
-        <f t="shared" si="26"/>
+      <c r="V24" s="6">
+        <f t="shared" si="22"/>
         <v>165</v>
       </c>
-      <c r="S24" s="6">
-        <f t="shared" si="26"/>
+      <c r="W24" s="6">
+        <f t="shared" si="22"/>
         <v>190</v>
       </c>
-      <c r="T24" s="6">
-        <f t="shared" si="26"/>
+      <c r="X24" s="6">
+        <f t="shared" si="22"/>
         <v>188</v>
       </c>
-      <c r="U24" s="6">
-        <f t="shared" si="26"/>
+      <c r="Y24" s="6">
+        <f t="shared" si="22"/>
         <v>149</v>
       </c>
-      <c r="V24" s="6">
-        <f t="shared" si="26"/>
-        <v>168.57999999999998</v>
-      </c>
-      <c r="W24" s="6">
-        <f t="shared" si="26"/>
-        <v>172.60740000000001</v>
-      </c>
-      <c r="X24" s="6">
-        <f t="shared" ref="X24:AF24" si="27">SUM(X21:X23)</f>
-        <v>177.78562200000002</v>
-      </c>
-      <c r="Y24" s="6">
-        <f t="shared" si="27"/>
-        <v>183.11919066000004</v>
-      </c>
       <c r="Z24" s="6">
-        <f t="shared" si="27"/>
-        <v>188.61276637980004</v>
+        <f t="shared" si="22"/>
+        <v>168</v>
       </c>
       <c r="AA24" s="6">
-        <f t="shared" si="27"/>
-        <v>194.27114937119404</v>
+        <f t="shared" si="22"/>
+        <v>176.13</v>
       </c>
       <c r="AB24" s="6">
-        <f t="shared" si="27"/>
-        <v>200.09928385232985</v>
+        <f t="shared" ref="AB24:AJ24" si="23">SUM(AB21:AB23)</f>
+        <v>181.41390000000001</v>
       </c>
       <c r="AC24" s="6">
-        <f t="shared" si="27"/>
-        <v>206.10226236789978</v>
+        <f t="shared" si="23"/>
+        <v>186.85631700000002</v>
       </c>
       <c r="AD24" s="6">
-        <f t="shared" si="27"/>
-        <v>212.28533023893675</v>
+        <f t="shared" si="23"/>
+        <v>192.46200651000001</v>
       </c>
       <c r="AE24" s="6">
-        <f t="shared" si="27"/>
-        <v>218.65389014610486</v>
+        <f t="shared" si="23"/>
+        <v>198.23586670530003</v>
       </c>
       <c r="AF24" s="6">
-        <f t="shared" si="27"/>
-        <v>225.21350685048799</v>
-      </c>
-    </row>
-    <row r="25" spans="2:143" s="2" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="23"/>
+        <v>204.18294270645902</v>
+      </c>
+      <c r="AG24" s="6">
+        <f t="shared" si="23"/>
+        <v>210.30843098765283</v>
+      </c>
+      <c r="AH24" s="6">
+        <f t="shared" si="23"/>
+        <v>216.61768391728242</v>
+      </c>
+      <c r="AI24" s="6">
+        <f t="shared" si="23"/>
+        <v>223.11621443480087</v>
+      </c>
+      <c r="AJ24" s="6">
+        <f t="shared" si="23"/>
+        <v>229.80970086784492</v>
+      </c>
+    </row>
+    <row r="25" spans="2:147" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>33</v>
       </c>
@@ -2541,107 +2708,111 @@
         <v>-388</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" ref="G25:L25" si="28">G20-G24</f>
+        <f t="shared" ref="G25:L25" si="24">G20-G24</f>
         <v>368</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>426</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>470</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>375</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>478</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>518</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" ref="M25:N25" si="29">M20-M24</f>
+        <f t="shared" ref="M25:N25" si="25">M20-M24</f>
         <v>484</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="29"/>
-        <v>472.62350000000004</v>
-      </c>
-      <c r="P25" s="9">
-        <f t="shared" ref="P25:W25" si="30">P20-P24</f>
+        <f t="shared" si="25"/>
+        <v>429</v>
+      </c>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="T25" s="9">
+        <f t="shared" ref="T25:AA25" si="26">T20-T24</f>
         <v>866</v>
       </c>
-      <c r="Q25" s="9">
-        <f t="shared" si="30"/>
+      <c r="U25" s="9">
+        <f t="shared" si="26"/>
         <v>781</v>
       </c>
-      <c r="R25" s="9">
-        <f t="shared" si="30"/>
+      <c r="V25" s="9">
+        <f t="shared" si="26"/>
         <v>967</v>
       </c>
-      <c r="S25" s="9">
-        <f t="shared" si="30"/>
+      <c r="W25" s="9">
+        <f t="shared" si="26"/>
         <v>886</v>
       </c>
-      <c r="T25" s="9">
-        <f t="shared" si="30"/>
+      <c r="X25" s="9">
+        <f t="shared" si="26"/>
         <v>403</v>
       </c>
-      <c r="U25" s="9">
-        <f t="shared" si="30"/>
+      <c r="Y25" s="9">
+        <f t="shared" si="26"/>
         <v>1639</v>
       </c>
-      <c r="V25" s="9">
-        <f t="shared" si="30"/>
-        <v>1952.6234999999988</v>
-      </c>
-      <c r="W25" s="9">
-        <f t="shared" si="30"/>
-        <v>2111.6637500000002</v>
-      </c>
-      <c r="X25" s="9">
-        <f t="shared" ref="X25:AF25" si="31">X20-X24</f>
-        <v>2218.9822899999999</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="31"/>
-        <v>2296.3952618600001</v>
-      </c>
       <c r="Z25" s="9">
-        <f t="shared" si="31"/>
-        <v>2340.6362173306002</v>
+        <f t="shared" si="26"/>
+        <v>1909</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="31"/>
-        <v>2385.7084985748138</v>
+        <f t="shared" si="26"/>
+        <v>1970.7695999999996</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="31"/>
-        <v>2405.680160573138</v>
+        <f t="shared" ref="AB25:AJ25" si="27">AB20-AB24</f>
+        <v>2040.4460880000001</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="31"/>
-        <v>2425.734976501823</v>
+        <f t="shared" si="27"/>
+        <v>2112.4203026399996</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="31"/>
-        <v>2445.8702810194827</v>
+        <f t="shared" si="27"/>
+        <v>2152.9855997028003</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="31"/>
-        <v>2466.0832772248982</v>
+        <f t="shared" si="27"/>
+        <v>2194.3080003535561</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="31"/>
-        <v>2486.3710321942258</v>
-      </c>
-    </row>
-    <row r="26" spans="2:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="27"/>
+        <v>2212.2863630229854</v>
+      </c>
+      <c r="AG25" s="9">
+        <f t="shared" si="27"/>
+        <v>2230.325567799086</v>
+      </c>
+      <c r="AH25" s="9">
+        <f t="shared" si="27"/>
+        <v>2248.4226548573242</v>
+      </c>
+      <c r="AI25" s="9">
+        <f t="shared" si="27"/>
+        <v>2266.5745277275514</v>
+      </c>
+      <c r="AJ25" s="9">
+        <f t="shared" si="27"/>
+        <v>2284.777948716131</v>
+      </c>
+    </row>
+    <row r="26" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
@@ -2661,7 +2832,7 @@
         <v>108</v>
       </c>
       <c r="J26" s="6">
-        <f t="shared" ref="J26:J27" si="32">U26-I26-H26-G26</f>
+        <f t="shared" ref="J26:J27" si="28">Y26-I26-H26-G26</f>
         <v>93</v>
       </c>
       <c r="K26" s="6">
@@ -2674,73 +2845,76 @@
         <v>115</v>
       </c>
       <c r="N26" s="6">
-        <f t="shared" ref="N26" si="33">N25*0.22</f>
-        <v>103.97717000000002</v>
-      </c>
-      <c r="P26" s="6">
+        <v>94</v>
+      </c>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="T26" s="6">
         <v>196</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="U26" s="6">
         <v>152</v>
       </c>
-      <c r="R26" s="6">
+      <c r="V26" s="6">
         <v>208</v>
       </c>
-      <c r="S26" s="6">
+      <c r="W26" s="6">
         <v>193</v>
       </c>
-      <c r="T26" s="6">
+      <c r="X26" s="6">
         <v>195</v>
       </c>
-      <c r="U26" s="6">
+      <c r="Y26" s="6">
         <v>388</v>
       </c>
-      <c r="V26" s="6">
-        <f t="shared" ref="V26:V27" si="34">SUM(K26:N26)</f>
-        <v>456.97717</v>
-      </c>
-      <c r="W26" s="6">
-        <f>W25*0.23</f>
-        <v>485.68266250000005</v>
-      </c>
-      <c r="X26" s="6">
-        <f t="shared" ref="X26:AF26" si="35">X25*0.23</f>
-        <v>510.36592669999999</v>
-      </c>
-      <c r="Y26" s="6">
-        <f t="shared" si="35"/>
-        <v>528.17091022780005</v>
-      </c>
       <c r="Z26" s="6">
-        <f t="shared" si="35"/>
-        <v>538.34632998603809</v>
+        <f t="shared" ref="Z26:Z27" si="29">SUM(K26:N26)</f>
+        <v>447</v>
       </c>
       <c r="AA26" s="6">
-        <f t="shared" si="35"/>
-        <v>548.71295467220716</v>
+        <f>AA25*0.23</f>
+        <v>453.27700799999991</v>
       </c>
       <c r="AB26" s="6">
-        <f t="shared" si="35"/>
-        <v>553.30643693182174</v>
+        <f t="shared" ref="AB26:AJ26" si="30">AB25*0.23</f>
+        <v>469.30260024000006</v>
       </c>
       <c r="AC26" s="6">
-        <f t="shared" si="35"/>
-        <v>557.91904459541934</v>
+        <f t="shared" si="30"/>
+        <v>485.85666960719993</v>
       </c>
       <c r="AD26" s="6">
-        <f t="shared" si="35"/>
-        <v>562.55016463448101</v>
+        <f t="shared" si="30"/>
+        <v>495.18668793164409</v>
       </c>
       <c r="AE26" s="6">
-        <f t="shared" si="35"/>
-        <v>567.19915376172662</v>
+        <f t="shared" si="30"/>
+        <v>504.6908400813179</v>
       </c>
       <c r="AF26" s="6">
-        <f t="shared" si="35"/>
-        <v>571.865337404672</v>
-      </c>
-    </row>
-    <row r="27" spans="2:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="30"/>
+        <v>508.82586349528668</v>
+      </c>
+      <c r="AG26" s="6">
+        <f t="shared" si="30"/>
+        <v>512.97488059378975</v>
+      </c>
+      <c r="AH26" s="6">
+        <f t="shared" si="30"/>
+        <v>517.13721061718456</v>
+      </c>
+      <c r="AI26" s="6">
+        <f t="shared" si="30"/>
+        <v>521.31214137733684</v>
+      </c>
+      <c r="AJ26" s="6">
+        <f t="shared" si="30"/>
+        <v>525.49892820471018</v>
+      </c>
+    </row>
+    <row r="27" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>35</v>
       </c>
@@ -2760,7 +2934,7 @@
         <v>-2</v>
       </c>
       <c r="J27" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="28"/>
         <v>-2</v>
       </c>
       <c r="K27" s="6">
@@ -2773,41 +2947,33 @@
         <v>2</v>
       </c>
       <c r="N27" s="6">
-        <v>0</v>
-      </c>
-      <c r="P27" s="6">
+        <v>8</v>
+      </c>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
+      <c r="T27" s="6">
         <v>3</v>
       </c>
-      <c r="Q27" s="6">
+      <c r="U27" s="6">
         <v>1</v>
       </c>
-      <c r="R27" s="6">
+      <c r="V27" s="6">
         <v>6</v>
       </c>
-      <c r="S27" s="6">
+      <c r="W27" s="6">
         <v>8</v>
       </c>
-      <c r="T27" s="6">
+      <c r="X27" s="6">
         <v>9</v>
       </c>
-      <c r="U27" s="6">
+      <c r="Y27" s="6">
         <v>-3</v>
       </c>
-      <c r="V27" s="6">
-        <f t="shared" si="34"/>
-        <v>6</v>
-      </c>
-      <c r="W27" s="6">
-        <v>0</v>
-      </c>
-      <c r="X27" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="6">
-        <v>0</v>
-      </c>
       <c r="Z27" s="6">
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>14</v>
       </c>
       <c r="AA27" s="6">
         <v>0</v>
@@ -2827,8 +2993,20 @@
       <c r="AF27" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="2:143" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AG27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:147" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
@@ -2841,551 +3019,555 @@
         <v>-399</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" ref="G28:L28" si="36">G25-G26-G27</f>
+        <f t="shared" ref="G28:L28" si="31">G25-G26-G27</f>
         <v>284</v>
       </c>
       <c r="H28" s="9">
+        <f t="shared" si="31"/>
+        <v>322</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="31"/>
+        <v>364</v>
+      </c>
+      <c r="J28" s="9">
+        <f t="shared" si="31"/>
+        <v>284</v>
+      </c>
+      <c r="K28" s="9">
+        <f t="shared" si="31"/>
+        <v>363</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" si="31"/>
+        <v>391</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" ref="M28:N28" si="32">M25-M26-M27</f>
+        <v>367</v>
+      </c>
+      <c r="N28" s="9">
+        <f t="shared" si="32"/>
+        <v>327</v>
+      </c>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="T28" s="9">
+        <f t="shared" ref="T28:AA28" si="33">T25-T26-T27</f>
+        <v>667</v>
+      </c>
+      <c r="U28" s="9">
+        <f t="shared" si="33"/>
+        <v>628</v>
+      </c>
+      <c r="V28" s="9">
+        <f t="shared" si="33"/>
+        <v>753</v>
+      </c>
+      <c r="W28" s="9">
+        <f t="shared" si="33"/>
+        <v>685</v>
+      </c>
+      <c r="X28" s="9">
+        <f t="shared" si="33"/>
+        <v>199</v>
+      </c>
+      <c r="Y28" s="9">
+        <f t="shared" si="33"/>
+        <v>1254</v>
+      </c>
+      <c r="Z28" s="9">
+        <f t="shared" si="33"/>
+        <v>1448</v>
+      </c>
+      <c r="AA28" s="9">
+        <f t="shared" si="33"/>
+        <v>1517.4925919999996</v>
+      </c>
+      <c r="AB28" s="9">
+        <f t="shared" ref="AB28:AJ28" si="34">AB25-AB26-AB27</f>
+        <v>1571.14348776</v>
+      </c>
+      <c r="AC28" s="9">
+        <f t="shared" si="34"/>
+        <v>1626.5636330327998</v>
+      </c>
+      <c r="AD28" s="9">
+        <f t="shared" si="34"/>
+        <v>1657.7989117711563</v>
+      </c>
+      <c r="AE28" s="9">
+        <f t="shared" si="34"/>
+        <v>1689.6171602722382</v>
+      </c>
+      <c r="AF28" s="9">
+        <f t="shared" si="34"/>
+        <v>1703.4604995276986</v>
+      </c>
+      <c r="AG28" s="9">
+        <f t="shared" si="34"/>
+        <v>1717.3506872052963</v>
+      </c>
+      <c r="AH28" s="9">
+        <f t="shared" si="34"/>
+        <v>1731.2854442401397</v>
+      </c>
+      <c r="AI28" s="9">
+        <f t="shared" si="34"/>
+        <v>1745.2623863502145</v>
+      </c>
+      <c r="AJ28" s="9">
+        <f t="shared" si="34"/>
+        <v>1759.2790205114209</v>
+      </c>
+      <c r="AK28" s="2">
+        <f>AJ28*(1+$AM$33)</f>
+        <v>1741.6862303063067</v>
+      </c>
+      <c r="AL28" s="2">
+        <f t="shared" ref="AL28:CW28" si="35">AK28*(1+$AM$33)</f>
+        <v>1724.2693680032437</v>
+      </c>
+      <c r="AM28" s="2">
+        <f t="shared" si="35"/>
+        <v>1707.0266743232112</v>
+      </c>
+      <c r="AN28" s="2">
+        <f t="shared" si="35"/>
+        <v>1689.956407579979</v>
+      </c>
+      <c r="AO28" s="2">
+        <f t="shared" si="35"/>
+        <v>1673.0568435041791</v>
+      </c>
+      <c r="AP28" s="2">
+        <f t="shared" si="35"/>
+        <v>1656.3262750691374</v>
+      </c>
+      <c r="AQ28" s="2">
+        <f t="shared" si="35"/>
+        <v>1639.763012318446</v>
+      </c>
+      <c r="AR28" s="2">
+        <f t="shared" si="35"/>
+        <v>1623.3653821952616</v>
+      </c>
+      <c r="AS28" s="2">
+        <f t="shared" si="35"/>
+        <v>1607.131728373309</v>
+      </c>
+      <c r="AT28" s="2">
+        <f t="shared" si="35"/>
+        <v>1591.0604110895758</v>
+      </c>
+      <c r="AU28" s="2">
+        <f t="shared" si="35"/>
+        <v>1575.1498069786801</v>
+      </c>
+      <c r="AV28" s="2">
+        <f t="shared" si="35"/>
+        <v>1559.3983089088933</v>
+      </c>
+      <c r="AW28" s="2">
+        <f t="shared" si="35"/>
+        <v>1543.8043258198045</v>
+      </c>
+      <c r="AX28" s="2">
+        <f t="shared" si="35"/>
+        <v>1528.3662825616063</v>
+      </c>
+      <c r="AY28" s="2">
+        <f t="shared" si="35"/>
+        <v>1513.0826197359902</v>
+      </c>
+      <c r="AZ28" s="2">
+        <f t="shared" si="35"/>
+        <v>1497.9517935386302</v>
+      </c>
+      <c r="BA28" s="2">
+        <f t="shared" si="35"/>
+        <v>1482.9722756032438</v>
+      </c>
+      <c r="BB28" s="2">
+        <f t="shared" si="35"/>
+        <v>1468.1425528472114</v>
+      </c>
+      <c r="BC28" s="2">
+        <f t="shared" si="35"/>
+        <v>1453.4611273187393</v>
+      </c>
+      <c r="BD28" s="2">
+        <f t="shared" si="35"/>
+        <v>1438.9265160455518</v>
+      </c>
+      <c r="BE28" s="2">
+        <f t="shared" si="35"/>
+        <v>1424.5372508850962</v>
+      </c>
+      <c r="BF28" s="2">
+        <f t="shared" si="35"/>
+        <v>1410.2918783762452</v>
+      </c>
+      <c r="BG28" s="2">
+        <f t="shared" si="35"/>
+        <v>1396.1889595924827</v>
+      </c>
+      <c r="BH28" s="2">
+        <f t="shared" si="35"/>
+        <v>1382.2270699965579</v>
+      </c>
+      <c r="BI28" s="2">
+        <f t="shared" si="35"/>
+        <v>1368.4047992965923</v>
+      </c>
+      <c r="BJ28" s="2">
+        <f t="shared" si="35"/>
+        <v>1354.7207513036262</v>
+      </c>
+      <c r="BK28" s="2">
+        <f t="shared" si="35"/>
+        <v>1341.17354379059</v>
+      </c>
+      <c r="BL28" s="2">
+        <f t="shared" si="35"/>
+        <v>1327.7618083526841</v>
+      </c>
+      <c r="BM28" s="2">
+        <f t="shared" si="35"/>
+        <v>1314.4841902691571</v>
+      </c>
+      <c r="BN28" s="2">
+        <f t="shared" si="35"/>
+        <v>1301.3393483664656</v>
+      </c>
+      <c r="BO28" s="2">
+        <f t="shared" si="35"/>
+        <v>1288.3259548828009</v>
+      </c>
+      <c r="BP28" s="2">
+        <f t="shared" si="35"/>
+        <v>1275.442695333973</v>
+      </c>
+      <c r="BQ28" s="2">
+        <f t="shared" si="35"/>
+        <v>1262.6882683806332</v>
+      </c>
+      <c r="BR28" s="2">
+        <f t="shared" si="35"/>
+        <v>1250.0613856968268</v>
+      </c>
+      <c r="BS28" s="2">
+        <f t="shared" si="35"/>
+        <v>1237.5607718398585</v>
+      </c>
+      <c r="BT28" s="2">
+        <f t="shared" si="35"/>
+        <v>1225.1851641214598</v>
+      </c>
+      <c r="BU28" s="2">
+        <f t="shared" si="35"/>
+        <v>1212.9333124802451</v>
+      </c>
+      <c r="BV28" s="2">
+        <f t="shared" si="35"/>
+        <v>1200.8039793554426</v>
+      </c>
+      <c r="BW28" s="2">
+        <f t="shared" si="35"/>
+        <v>1188.7959395618882</v>
+      </c>
+      <c r="BX28" s="2">
+        <f t="shared" si="35"/>
+        <v>1176.9079801662692</v>
+      </c>
+      <c r="BY28" s="2">
+        <f t="shared" si="35"/>
+        <v>1165.1389003646066</v>
+      </c>
+      <c r="BZ28" s="2">
+        <f t="shared" si="35"/>
+        <v>1153.4875113609605</v>
+      </c>
+      <c r="CA28" s="2">
+        <f t="shared" si="35"/>
+        <v>1141.9526362473509</v>
+      </c>
+      <c r="CB28" s="2">
+        <f t="shared" si="35"/>
+        <v>1130.5331098848774</v>
+      </c>
+      <c r="CC28" s="2">
+        <f t="shared" si="35"/>
+        <v>1119.2277787860287</v>
+      </c>
+      <c r="CD28" s="2">
+        <f t="shared" si="35"/>
+        <v>1108.0355009981683</v>
+      </c>
+      <c r="CE28" s="2">
+        <f t="shared" si="35"/>
+        <v>1096.9551459881866</v>
+      </c>
+      <c r="CF28" s="2">
+        <f t="shared" si="35"/>
+        <v>1085.9855945283048</v>
+      </c>
+      <c r="CG28" s="2">
+        <f t="shared" si="35"/>
+        <v>1075.1257385830218</v>
+      </c>
+      <c r="CH28" s="2">
+        <f t="shared" si="35"/>
+        <v>1064.3744811971915</v>
+      </c>
+      <c r="CI28" s="2">
+        <f t="shared" si="35"/>
+        <v>1053.7307363852196</v>
+      </c>
+      <c r="CJ28" s="2">
+        <f t="shared" si="35"/>
+        <v>1043.1934290213674</v>
+      </c>
+      <c r="CK28" s="2">
+        <f t="shared" si="35"/>
+        <v>1032.7614947311538</v>
+      </c>
+      <c r="CL28" s="2">
+        <f t="shared" si="35"/>
+        <v>1022.4338797838423</v>
+      </c>
+      <c r="CM28" s="2">
+        <f t="shared" si="35"/>
+        <v>1012.2095409860038</v>
+      </c>
+      <c r="CN28" s="2">
+        <f t="shared" si="35"/>
+        <v>1002.0874455761438</v>
+      </c>
+      <c r="CO28" s="2">
+        <f t="shared" si="35"/>
+        <v>992.06657112038226</v>
+      </c>
+      <c r="CP28" s="2">
+        <f t="shared" si="35"/>
+        <v>982.14590540917845</v>
+      </c>
+      <c r="CQ28" s="2">
+        <f t="shared" si="35"/>
+        <v>972.32444635508671</v>
+      </c>
+      <c r="CR28" s="2">
+        <f t="shared" si="35"/>
+        <v>962.60120189153588</v>
+      </c>
+      <c r="CS28" s="2">
+        <f t="shared" si="35"/>
+        <v>952.97518987262049</v>
+      </c>
+      <c r="CT28" s="2">
+        <f t="shared" si="35"/>
+        <v>943.44543797389429</v>
+      </c>
+      <c r="CU28" s="2">
+        <f t="shared" si="35"/>
+        <v>934.01098359415539</v>
+      </c>
+      <c r="CV28" s="2">
+        <f t="shared" si="35"/>
+        <v>924.67087375821382</v>
+      </c>
+      <c r="CW28" s="2">
+        <f t="shared" si="35"/>
+        <v>915.42416502063168</v>
+      </c>
+      <c r="CX28" s="2">
+        <f t="shared" ref="CX28:EQ28" si="36">CW28*(1+$AM$33)</f>
+        <v>906.26992337042532</v>
+      </c>
+      <c r="CY28" s="2">
         <f t="shared" si="36"/>
-        <v>322</v>
-      </c>
-      <c r="I28" s="9">
+        <v>897.20722413672104</v>
+      </c>
+      <c r="CZ28" s="2">
         <f t="shared" si="36"/>
-        <v>364</v>
-      </c>
-      <c r="J28" s="9">
+        <v>888.23515189535385</v>
+      </c>
+      <c r="DA28" s="2">
         <f t="shared" si="36"/>
-        <v>284</v>
-      </c>
-      <c r="K28" s="9">
+        <v>879.3528003764003</v>
+      </c>
+      <c r="DB28" s="2">
         <f t="shared" si="36"/>
-        <v>363</v>
-      </c>
-      <c r="L28" s="9">
+        <v>870.55927237263631</v>
+      </c>
+      <c r="DC28" s="2">
         <f t="shared" si="36"/>
-        <v>391</v>
-      </c>
-      <c r="M28" s="9">
-        <f t="shared" ref="M28:N28" si="37">M25-M26-M27</f>
-        <v>367</v>
-      </c>
-      <c r="N28" s="9">
-        <f t="shared" si="37"/>
-        <v>368.64633000000003</v>
-      </c>
-      <c r="P28" s="9">
-        <f t="shared" ref="P28:W28" si="38">P25-P26-P27</f>
-        <v>667</v>
-      </c>
-      <c r="Q28" s="9">
-        <f t="shared" si="38"/>
-        <v>628</v>
-      </c>
-      <c r="R28" s="9">
-        <f t="shared" si="38"/>
-        <v>753</v>
-      </c>
-      <c r="S28" s="9">
-        <f t="shared" si="38"/>
-        <v>685</v>
-      </c>
-      <c r="T28" s="9">
-        <f t="shared" si="38"/>
-        <v>199</v>
-      </c>
-      <c r="U28" s="9">
-        <f t="shared" si="38"/>
-        <v>1254</v>
-      </c>
-      <c r="V28" s="9">
-        <f t="shared" si="38"/>
-        <v>1489.6463299999987</v>
-      </c>
-      <c r="W28" s="9">
-        <f t="shared" si="38"/>
-        <v>1625.9810875000001</v>
-      </c>
-      <c r="X28" s="9">
-        <f t="shared" ref="X28:AF28" si="39">X25-X26-X27</f>
-        <v>1708.6163632999999</v>
-      </c>
-      <c r="Y28" s="9">
-        <f t="shared" si="39"/>
-        <v>1768.2243516322001</v>
-      </c>
-      <c r="Z28" s="9">
-        <f t="shared" si="39"/>
-        <v>1802.289887344562</v>
-      </c>
-      <c r="AA28" s="9">
-        <f t="shared" si="39"/>
-        <v>1836.9955439026066</v>
-      </c>
-      <c r="AB28" s="9">
-        <f t="shared" si="39"/>
-        <v>1852.3737236413162</v>
-      </c>
-      <c r="AC28" s="9">
-        <f t="shared" si="39"/>
-        <v>1867.8159319064036</v>
-      </c>
-      <c r="AD28" s="9">
-        <f t="shared" si="39"/>
-        <v>1883.3201163850017</v>
-      </c>
-      <c r="AE28" s="9">
-        <f t="shared" si="39"/>
-        <v>1898.8841234631716</v>
-      </c>
-      <c r="AF28" s="9">
-        <f t="shared" si="39"/>
-        <v>1914.5056947895537</v>
-      </c>
-      <c r="AG28" s="2">
-        <f>AF28*(1+$AI$33)</f>
-        <v>1895.3606378416582</v>
-      </c>
-      <c r="AH28" s="2">
-        <f t="shared" ref="AH28:CS28" si="40">AG28*(1+$AI$33)</f>
-        <v>1876.4070314632415</v>
-      </c>
-      <c r="AI28" s="2">
-        <f t="shared" si="40"/>
-        <v>1857.6429611486092</v>
-      </c>
-      <c r="AJ28" s="2">
-        <f t="shared" si="40"/>
-        <v>1839.066531537123</v>
-      </c>
-      <c r="AK28" s="2">
-        <f t="shared" si="40"/>
-        <v>1820.6758662217517</v>
-      </c>
-      <c r="AL28" s="2">
-        <f t="shared" si="40"/>
-        <v>1802.4691075595342</v>
-      </c>
-      <c r="AM28" s="2">
-        <f t="shared" si="40"/>
-        <v>1784.4444164839388</v>
-      </c>
-      <c r="AN28" s="2">
-        <f t="shared" si="40"/>
-        <v>1766.5999723190994</v>
-      </c>
-      <c r="AO28" s="2">
-        <f t="shared" si="40"/>
-        <v>1748.9339725959085</v>
-      </c>
-      <c r="AP28" s="2">
-        <f t="shared" si="40"/>
-        <v>1731.4446328699494</v>
-      </c>
-      <c r="AQ28" s="2">
-        <f t="shared" si="40"/>
-        <v>1714.1301865412499</v>
-      </c>
-      <c r="AR28" s="2">
-        <f t="shared" si="40"/>
-        <v>1696.9888846758374</v>
-      </c>
-      <c r="AS28" s="2">
-        <f t="shared" si="40"/>
-        <v>1680.0189958290791</v>
-      </c>
-      <c r="AT28" s="2">
-        <f t="shared" si="40"/>
-        <v>1663.2188058707884</v>
-      </c>
-      <c r="AU28" s="2">
-        <f t="shared" si="40"/>
-        <v>1646.5866178120805</v>
-      </c>
-      <c r="AV28" s="2">
-        <f t="shared" si="40"/>
-        <v>1630.1207516339596</v>
-      </c>
-      <c r="AW28" s="2">
-        <f t="shared" si="40"/>
-        <v>1613.8195441176199</v>
-      </c>
-      <c r="AX28" s="2">
-        <f t="shared" si="40"/>
-        <v>1597.6813486764436</v>
-      </c>
-      <c r="AY28" s="2">
-        <f t="shared" si="40"/>
-        <v>1581.7045351896791</v>
-      </c>
-      <c r="AZ28" s="2">
-        <f t="shared" si="40"/>
-        <v>1565.8874898377824</v>
-      </c>
-      <c r="BA28" s="2">
-        <f t="shared" si="40"/>
-        <v>1550.2286149394045</v>
-      </c>
-      <c r="BB28" s="2">
-        <f t="shared" si="40"/>
-        <v>1534.7263287900105</v>
-      </c>
-      <c r="BC28" s="2">
-        <f t="shared" si="40"/>
-        <v>1519.3790655021103</v>
-      </c>
-      <c r="BD28" s="2">
-        <f t="shared" si="40"/>
-        <v>1504.1852748470892</v>
-      </c>
-      <c r="BE28" s="2">
-        <f t="shared" si="40"/>
-        <v>1489.1434220986182</v>
-      </c>
-      <c r="BF28" s="2">
-        <f t="shared" si="40"/>
-        <v>1474.251987877632</v>
-      </c>
-      <c r="BG28" s="2">
-        <f t="shared" si="40"/>
-        <v>1459.5094679988556</v>
-      </c>
-      <c r="BH28" s="2">
-        <f t="shared" si="40"/>
-        <v>1444.9143733188671</v>
-      </c>
-      <c r="BI28" s="2">
-        <f t="shared" si="40"/>
-        <v>1430.4652295856783</v>
-      </c>
-      <c r="BJ28" s="2">
-        <f t="shared" si="40"/>
-        <v>1416.1605772898215</v>
-      </c>
-      <c r="BK28" s="2">
-        <f t="shared" si="40"/>
-        <v>1401.9989715169233</v>
-      </c>
-      <c r="BL28" s="2">
-        <f t="shared" si="40"/>
-        <v>1387.9789818017541</v>
-      </c>
-      <c r="BM28" s="2">
-        <f t="shared" si="40"/>
-        <v>1374.0991919837365</v>
-      </c>
-      <c r="BN28" s="2">
-        <f t="shared" si="40"/>
-        <v>1360.3582000638992</v>
-      </c>
-      <c r="BO28" s="2">
-        <f t="shared" si="40"/>
-        <v>1346.7546180632601</v>
-      </c>
-      <c r="BP28" s="2">
-        <f t="shared" si="40"/>
-        <v>1333.2870718826275</v>
-      </c>
-      <c r="BQ28" s="2">
-        <f t="shared" si="40"/>
-        <v>1319.9542011638011</v>
-      </c>
-      <c r="BR28" s="2">
-        <f t="shared" si="40"/>
-        <v>1306.7546591521632</v>
-      </c>
-      <c r="BS28" s="2">
-        <f t="shared" si="40"/>
-        <v>1293.6871125606415</v>
-      </c>
-      <c r="BT28" s="2">
-        <f t="shared" si="40"/>
-        <v>1280.7502414350352</v>
-      </c>
-      <c r="BU28" s="2">
-        <f t="shared" si="40"/>
-        <v>1267.9427390206847</v>
-      </c>
-      <c r="BV28" s="2">
-        <f t="shared" si="40"/>
-        <v>1255.2633116304778</v>
-      </c>
-      <c r="BW28" s="2">
-        <f t="shared" si="40"/>
-        <v>1242.710678514173</v>
-      </c>
-      <c r="BX28" s="2">
-        <f t="shared" si="40"/>
-        <v>1230.2835717290313</v>
-      </c>
-      <c r="BY28" s="2">
-        <f t="shared" si="40"/>
-        <v>1217.9807360117411</v>
-      </c>
-      <c r="BZ28" s="2">
-        <f t="shared" si="40"/>
-        <v>1205.8009286516237</v>
-      </c>
-      <c r="CA28" s="2">
-        <f t="shared" si="40"/>
-        <v>1193.7429193651076</v>
-      </c>
-      <c r="CB28" s="2">
-        <f t="shared" si="40"/>
-        <v>1181.8054901714565</v>
-      </c>
-      <c r="CC28" s="2">
-        <f t="shared" si="40"/>
-        <v>1169.987435269742</v>
-      </c>
-      <c r="CD28" s="2">
-        <f t="shared" si="40"/>
-        <v>1158.2875609170446</v>
-      </c>
-      <c r="CE28" s="2">
-        <f t="shared" si="40"/>
-        <v>1146.7046853078741</v>
-      </c>
-      <c r="CF28" s="2">
-        <f t="shared" si="40"/>
-        <v>1135.2376384547954</v>
-      </c>
-      <c r="CG28" s="2">
-        <f t="shared" si="40"/>
-        <v>1123.8852620702473</v>
-      </c>
-      <c r="CH28" s="2">
-        <f t="shared" si="40"/>
-        <v>1112.6464094495448</v>
-      </c>
-      <c r="CI28" s="2">
-        <f t="shared" si="40"/>
-        <v>1101.5199453550492</v>
-      </c>
-      <c r="CJ28" s="2">
-        <f t="shared" si="40"/>
-        <v>1090.5047459014988</v>
-      </c>
-      <c r="CK28" s="2">
-        <f t="shared" si="40"/>
-        <v>1079.5996984424839</v>
-      </c>
-      <c r="CL28" s="2">
-        <f t="shared" si="40"/>
-        <v>1068.8037014580591</v>
-      </c>
-      <c r="CM28" s="2">
-        <f t="shared" si="40"/>
-        <v>1058.1156644434784</v>
-      </c>
-      <c r="CN28" s="2">
-        <f t="shared" si="40"/>
-        <v>1047.5345077990437</v>
-      </c>
-      <c r="CO28" s="2">
-        <f t="shared" si="40"/>
-        <v>1037.0591627210533</v>
-      </c>
-      <c r="CP28" s="2">
-        <f t="shared" si="40"/>
-        <v>1026.6885710938427</v>
-      </c>
-      <c r="CQ28" s="2">
-        <f t="shared" si="40"/>
-        <v>1016.4216853829042</v>
-      </c>
-      <c r="CR28" s="2">
-        <f t="shared" si="40"/>
-        <v>1006.2574685290751</v>
-      </c>
-      <c r="CS28" s="2">
-        <f t="shared" si="40"/>
-        <v>996.19489384378437</v>
-      </c>
-      <c r="CT28" s="2">
-        <f t="shared" ref="CT28:EM28" si="41">CS28*(1+$AI$33)</f>
-        <v>986.23294490534647</v>
-      </c>
-      <c r="CU28" s="2">
-        <f t="shared" si="41"/>
-        <v>976.37061545629297</v>
-      </c>
-      <c r="CV28" s="2">
-        <f t="shared" si="41"/>
-        <v>966.60690930173007</v>
-      </c>
-      <c r="CW28" s="2">
-        <f t="shared" si="41"/>
-        <v>956.94084020871276</v>
-      </c>
-      <c r="CX28" s="2">
-        <f t="shared" si="41"/>
-        <v>947.37143180662565</v>
-      </c>
-      <c r="CY28" s="2">
-        <f t="shared" si="41"/>
-        <v>937.89771748855935</v>
-      </c>
-      <c r="CZ28" s="2">
-        <f t="shared" si="41"/>
-        <v>928.51874031367379</v>
-      </c>
-      <c r="DA28" s="2">
-        <f t="shared" si="41"/>
-        <v>919.23355291053701</v>
-      </c>
-      <c r="DB28" s="2">
-        <f t="shared" si="41"/>
-        <v>910.04121738143158</v>
-      </c>
-      <c r="DC28" s="2">
-        <f t="shared" si="41"/>
-        <v>900.94080520761725</v>
+        <v>861.85367964890997</v>
       </c>
       <c r="DD28" s="2">
-        <f t="shared" si="41"/>
-        <v>891.93139715554105</v>
+        <f t="shared" si="36"/>
+        <v>853.23514285242084</v>
       </c>
       <c r="DE28" s="2">
-        <f t="shared" si="41"/>
-        <v>883.01208318398562</v>
+        <f t="shared" si="36"/>
+        <v>844.70279142389666</v>
       </c>
       <c r="DF28" s="2">
-        <f t="shared" si="41"/>
-        <v>874.18196235214577</v>
+        <f t="shared" si="36"/>
+        <v>836.25576350965764</v>
       </c>
       <c r="DG28" s="2">
-        <f t="shared" si="41"/>
-        <v>865.44014272862432</v>
+        <f t="shared" si="36"/>
+        <v>827.89320587456109</v>
       </c>
       <c r="DH28" s="2">
-        <f t="shared" si="41"/>
-        <v>856.78574130133802</v>
+        <f t="shared" si="36"/>
+        <v>819.61427381581552</v>
       </c>
       <c r="DI28" s="2">
-        <f t="shared" si="41"/>
-        <v>848.21788388832465</v>
+        <f t="shared" si="36"/>
+        <v>811.41813107765734</v>
       </c>
       <c r="DJ28" s="2">
-        <f t="shared" si="41"/>
-        <v>839.73570504944144</v>
+        <f t="shared" si="36"/>
+        <v>803.30394976688081</v>
       </c>
       <c r="DK28" s="2">
-        <f t="shared" si="41"/>
-        <v>831.33834799894703</v>
+        <f t="shared" si="36"/>
+        <v>795.27091026921198</v>
       </c>
       <c r="DL28" s="2">
-        <f t="shared" si="41"/>
-        <v>823.02496451895752</v>
+        <f t="shared" si="36"/>
+        <v>787.31820116651988</v>
       </c>
       <c r="DM28" s="2">
-        <f t="shared" si="41"/>
-        <v>814.79471487376793</v>
+        <f t="shared" si="36"/>
+        <v>779.44501915485466</v>
       </c>
       <c r="DN28" s="2">
-        <f t="shared" si="41"/>
-        <v>806.64676772503026</v>
+        <f t="shared" si="36"/>
+        <v>771.65056896330611</v>
       </c>
       <c r="DO28" s="2">
-        <f t="shared" si="41"/>
-        <v>798.58030004777993</v>
+        <f t="shared" si="36"/>
+        <v>763.93406327367302</v>
       </c>
       <c r="DP28" s="2">
-        <f t="shared" si="41"/>
-        <v>790.59449704730207</v>
+        <f t="shared" si="36"/>
+        <v>756.29472264093624</v>
       </c>
       <c r="DQ28" s="2">
-        <f t="shared" si="41"/>
-        <v>782.68855207682907</v>
+        <f t="shared" si="36"/>
+        <v>748.73177541452685</v>
       </c>
       <c r="DR28" s="2">
-        <f t="shared" si="41"/>
-        <v>774.86166655606075</v>
+        <f t="shared" si="36"/>
+        <v>741.24445766038161</v>
       </c>
       <c r="DS28" s="2">
-        <f t="shared" si="41"/>
-        <v>767.11304989050018</v>
+        <f t="shared" si="36"/>
+        <v>733.83201308377784</v>
       </c>
       <c r="DT28" s="2">
-        <f t="shared" si="41"/>
-        <v>759.44191939159521</v>
+        <f t="shared" si="36"/>
+        <v>726.49369295294002</v>
       </c>
       <c r="DU28" s="2">
-        <f t="shared" si="41"/>
-        <v>751.84750019767921</v>
+        <f t="shared" si="36"/>
+        <v>719.2287560234106</v>
       </c>
       <c r="DV28" s="2">
-        <f t="shared" si="41"/>
-        <v>744.32902519570246</v>
+        <f t="shared" si="36"/>
+        <v>712.03646846317645</v>
       </c>
       <c r="DW28" s="2">
-        <f t="shared" si="41"/>
-        <v>736.88573494374543</v>
+        <f t="shared" si="36"/>
+        <v>704.91610377854465</v>
       </c>
       <c r="DX28" s="2">
-        <f t="shared" si="41"/>
-        <v>729.51687759430797</v>
+        <f t="shared" si="36"/>
+        <v>697.86694274075921</v>
       </c>
       <c r="DY28" s="2">
-        <f t="shared" si="41"/>
-        <v>722.22170881836485</v>
+        <f t="shared" si="36"/>
+        <v>690.88827331335165</v>
       </c>
       <c r="DZ28" s="2">
-        <f t="shared" si="41"/>
-        <v>714.99949173018115</v>
+        <f t="shared" si="36"/>
+        <v>683.97939058021814</v>
       </c>
       <c r="EA28" s="2">
-        <f t="shared" si="41"/>
-        <v>707.84949681287935</v>
+        <f t="shared" si="36"/>
+        <v>677.139596674416</v>
       </c>
       <c r="EB28" s="2">
-        <f t="shared" si="41"/>
-        <v>700.77100184475057</v>
+        <f t="shared" si="36"/>
+        <v>670.3682007076718</v>
       </c>
       <c r="EC28" s="2">
-        <f t="shared" si="41"/>
-        <v>693.76329182630309</v>
+        <f t="shared" si="36"/>
+        <v>663.66451870059507</v>
       </c>
       <c r="ED28" s="2">
-        <f t="shared" si="41"/>
-        <v>686.82565890804005</v>
+        <f t="shared" si="36"/>
+        <v>657.02787351358916</v>
       </c>
       <c r="EE28" s="2">
-        <f t="shared" si="41"/>
-        <v>679.95740231895968</v>
+        <f t="shared" si="36"/>
+        <v>650.45759477845331</v>
       </c>
       <c r="EF28" s="2">
-        <f t="shared" si="41"/>
-        <v>673.15782829577006</v>
+        <f t="shared" si="36"/>
+        <v>643.95301883066873</v>
       </c>
       <c r="EG28" s="2">
-        <f t="shared" si="41"/>
-        <v>666.42625001281237</v>
+        <f t="shared" si="36"/>
+        <v>637.51348864236206</v>
       </c>
       <c r="EH28" s="2">
-        <f t="shared" si="41"/>
-        <v>659.7619875126843</v>
+        <f t="shared" si="36"/>
+        <v>631.1383537559384</v>
       </c>
       <c r="EI28" s="2">
-        <f t="shared" si="41"/>
-        <v>653.16436763755746</v>
+        <f t="shared" si="36"/>
+        <v>624.82697021837896</v>
       </c>
       <c r="EJ28" s="2">
-        <f t="shared" si="41"/>
-        <v>646.63272396118191</v>
+        <f t="shared" si="36"/>
+        <v>618.57870051619511</v>
       </c>
       <c r="EK28" s="2">
-        <f t="shared" si="41"/>
-        <v>640.16639672157009</v>
+        <f t="shared" si="36"/>
+        <v>612.39291351103316</v>
       </c>
       <c r="EL28" s="2">
-        <f t="shared" si="41"/>
-        <v>633.76473275435444</v>
+        <f t="shared" si="36"/>
+        <v>606.26898437592286</v>
       </c>
       <c r="EM28" s="2">
-        <f t="shared" si="41"/>
-        <v>627.42708542681089</v>
-      </c>
-    </row>
-    <row r="29" spans="2:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="36"/>
+        <v>600.20629453216361</v>
+      </c>
+      <c r="EN28" s="2">
+        <f t="shared" si="36"/>
+        <v>594.20423158684196</v>
+      </c>
+      <c r="EO28" s="2">
+        <f t="shared" si="36"/>
+        <v>588.26218927097352</v>
+      </c>
+      <c r="EP28" s="2">
+        <f t="shared" si="36"/>
+        <v>582.3795673782638</v>
+      </c>
+      <c r="EQ28" s="2">
+        <f t="shared" si="36"/>
+        <v>576.55577170448112</v>
+      </c>
+    </row>
+    <row r="29" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>2</v>
       </c>
@@ -3398,27 +3580,27 @@
         <v>128.69999999999999</v>
       </c>
       <c r="G29" s="6">
-        <f t="shared" ref="G29:L29" si="42">128.7</f>
+        <f t="shared" ref="G29:L29" si="37">128.7</f>
         <v>128.69999999999999</v>
       </c>
       <c r="H29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>128.69999999999999</v>
       </c>
       <c r="I29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>128.69999999999999</v>
       </c>
       <c r="J29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>128.69999999999999</v>
       </c>
       <c r="K29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>128.69999999999999</v>
       </c>
       <c r="L29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>128.69999999999999</v>
       </c>
       <c r="M29" s="6">
@@ -3426,79 +3608,71 @@
         <v>127.9</v>
       </c>
       <c r="N29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
-      </c>
-      <c r="P29" s="6">
-        <f t="shared" ref="P29:U29" si="43">128.7</f>
+        <v>127</v>
+      </c>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="T29" s="6">
+        <f t="shared" ref="T29:Y29" si="38">128.7</f>
         <v>128.69999999999999</v>
       </c>
-      <c r="Q29" s="6">
-        <f t="shared" si="43"/>
+      <c r="U29" s="6">
+        <f t="shared" si="38"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="R29" s="6">
-        <f t="shared" si="43"/>
+      <c r="V29" s="6">
+        <f t="shared" si="38"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="S29" s="6">
-        <f t="shared" si="43"/>
+      <c r="W29" s="6">
+        <f t="shared" si="38"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="T29" s="6">
-        <f t="shared" si="43"/>
+      <c r="X29" s="6">
+        <f t="shared" si="38"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="U29" s="6">
-        <f t="shared" si="43"/>
+      <c r="Y29" s="6">
+        <f t="shared" si="38"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="V29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
-      </c>
-      <c r="W29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
-      </c>
-      <c r="X29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
-      </c>
-      <c r="Y29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
-      </c>
       <c r="Z29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
+        <v>127</v>
       </c>
       <c r="AA29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
+        <v>127</v>
       </c>
       <c r="AB29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
+        <v>127</v>
       </c>
       <c r="AC29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
+        <v>127</v>
       </c>
       <c r="AD29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
+        <v>127</v>
       </c>
       <c r="AE29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
+        <v>127</v>
       </c>
       <c r="AF29" s="6">
-        <f>127.9</f>
-        <v>127.9</v>
-      </c>
-    </row>
-    <row r="30" spans="2:143" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+      <c r="AG29" s="6">
+        <v>127</v>
+      </c>
+      <c r="AH29" s="6">
+        <v>127</v>
+      </c>
+      <c r="AI29" s="6">
+        <v>127</v>
+      </c>
+      <c r="AJ29" s="6">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
@@ -3511,107 +3685,111 @@
         <v>-3.1002331002331007</v>
       </c>
       <c r="G30" s="8">
-        <f t="shared" ref="G30:L30" si="44">G28/G29</f>
+        <f t="shared" ref="G30:L30" si="39">G28/G29</f>
         <v>2.2066822066822067</v>
       </c>
       <c r="H30" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="39"/>
         <v>2.5019425019425023</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="39"/>
         <v>2.8282828282828287</v>
       </c>
       <c r="J30" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="39"/>
         <v>2.2066822066822067</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="39"/>
         <v>2.8205128205128207</v>
       </c>
       <c r="L30" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="39"/>
         <v>3.0380730380730383</v>
       </c>
       <c r="M30" s="8">
-        <f t="shared" ref="M30:N30" si="45">M28/M29</f>
+        <f t="shared" ref="M30:N30" si="40">M28/M29</f>
         <v>2.8694292415949958</v>
       </c>
       <c r="N30" s="8">
-        <f t="shared" si="45"/>
-        <v>2.882301250977326</v>
-      </c>
-      <c r="P30" s="8">
-        <f t="shared" ref="P30:W30" si="46">P28/P29</f>
+        <f t="shared" si="40"/>
+        <v>2.5748031496062991</v>
+      </c>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="T30" s="8">
+        <f t="shared" ref="T30:AA30" si="41">T28/T29</f>
         <v>5.1825951825951835</v>
       </c>
-      <c r="Q30" s="8">
-        <f t="shared" si="46"/>
+      <c r="U30" s="8">
+        <f t="shared" si="41"/>
         <v>4.8795648795648798</v>
       </c>
-      <c r="R30" s="8">
-        <f t="shared" si="46"/>
+      <c r="V30" s="8">
+        <f t="shared" si="41"/>
         <v>5.8508158508158514</v>
       </c>
-      <c r="S30" s="8">
-        <f t="shared" si="46"/>
+      <c r="W30" s="8">
+        <f t="shared" si="41"/>
         <v>5.3224553224553226</v>
       </c>
-      <c r="T30" s="8">
-        <f t="shared" si="46"/>
+      <c r="X30" s="8">
+        <f t="shared" si="41"/>
         <v>1.5462315462315463</v>
       </c>
-      <c r="U30" s="8">
-        <f t="shared" si="46"/>
+      <c r="Y30" s="8">
+        <f t="shared" si="41"/>
         <v>9.7435897435897445</v>
       </c>
-      <c r="V30" s="8">
-        <f t="shared" si="46"/>
-        <v>11.646961141516799</v>
-      </c>
-      <c r="W30" s="8">
-        <f t="shared" si="46"/>
-        <v>12.712909206411259</v>
-      </c>
-      <c r="X30" s="8">
-        <f t="shared" ref="X30:AF30" si="47">X28/X29</f>
-        <v>13.359002058639561</v>
-      </c>
-      <c r="Y30" s="8">
-        <f t="shared" si="47"/>
-        <v>13.825053570228304</v>
-      </c>
       <c r="Z30" s="8">
-        <f t="shared" si="47"/>
-        <v>14.09139865007476</v>
+        <f t="shared" si="41"/>
+        <v>11.401574803149606</v>
       </c>
       <c r="AA30" s="8">
-        <f t="shared" si="47"/>
-        <v>14.362748584070419</v>
+        <f t="shared" si="41"/>
+        <v>11.948760566929131</v>
       </c>
       <c r="AB30" s="8">
-        <f t="shared" si="47"/>
-        <v>14.482984547625614</v>
+        <f t="shared" ref="AB30:AJ30" si="42">AB28/AB29</f>
+        <v>12.371208565039369</v>
       </c>
       <c r="AC30" s="8">
-        <f t="shared" si="47"/>
-        <v>14.6037211251478</v>
+        <f t="shared" si="42"/>
+        <v>12.807587661675589</v>
       </c>
       <c r="AD30" s="8">
-        <f t="shared" si="47"/>
-        <v>14.724942270406581</v>
+        <f t="shared" si="42"/>
+        <v>13.053534738355562</v>
       </c>
       <c r="AE30" s="8">
-        <f t="shared" si="47"/>
-        <v>14.846631145138167</v>
+        <f t="shared" si="42"/>
+        <v>13.30407212812786</v>
       </c>
       <c r="AF30" s="8">
-        <f t="shared" si="47"/>
-        <v>14.968770092177902</v>
-      </c>
-    </row>
-    <row r="32" spans="2:143" x14ac:dyDescent="0.3">
+        <f t="shared" si="42"/>
+        <v>13.413074799430698</v>
+      </c>
+      <c r="AG30" s="8">
+        <f t="shared" si="42"/>
+        <v>13.522446355947215</v>
+      </c>
+      <c r="AH30" s="8">
+        <f t="shared" si="42"/>
+        <v>13.632168852284565</v>
+      </c>
+      <c r="AI30" s="8">
+        <f t="shared" si="42"/>
+        <v>13.742223514568618</v>
+      </c>
+      <c r="AJ30" s="8">
+        <f t="shared" si="42"/>
+        <v>13.852590712688354</v>
+      </c>
+    </row>
+    <row r="32" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>40</v>
       </c>
@@ -3620,11 +3798,11 @@
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10">
-        <f t="shared" ref="H32:I32" si="48">H13/D13-1</f>
+        <f t="shared" ref="H32:I32" si="43">H13/D13-1</f>
         <v>7.6602397081813489E-2</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>6.8604947717419096E-2</v>
       </c>
       <c r="J32" s="10"/>
@@ -3633,110 +3811,114 @@
         <v>6.7924528301886777E-2</v>
       </c>
       <c r="L32" s="10">
-        <f t="shared" ref="L32:N32" si="49">L13/H13-1</f>
+        <f t="shared" ref="L32:N32" si="44">L13/H13-1</f>
         <v>2.9283639883833423E-2</v>
       </c>
       <c r="M32" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>6.658711217183777E-2</v>
       </c>
       <c r="N32" s="10">
-        <f t="shared" si="49"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
+        <f t="shared" si="44"/>
+        <v>-3.6197021764032056E-2</v>
+      </c>
+      <c r="O32" s="10"/>
       <c r="P32" s="10"/>
-      <c r="Q32" s="10">
-        <f>Q13/P13-1</f>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="T32" s="10"/>
+      <c r="U32" s="10">
+        <f>U13/T13-1</f>
         <v>0.10843699296917242</v>
       </c>
-      <c r="R32" s="10">
-        <f t="shared" ref="R32:AF32" si="50">R13/Q13-1</f>
+      <c r="V32" s="10">
+        <f t="shared" ref="V32:AJ32" si="45">V13/U13-1</f>
         <v>0.11710173212978781</v>
       </c>
-      <c r="S32" s="10">
-        <f t="shared" si="50"/>
+      <c r="W32" s="10">
+        <f t="shared" si="45"/>
         <v>4.797262866710339E-2</v>
       </c>
-      <c r="T32" s="10">
-        <f t="shared" si="50"/>
+      <c r="X32" s="10">
+        <f t="shared" si="45"/>
         <v>7.2381217004723553E-2</v>
       </c>
-      <c r="U32" s="10">
-        <f t="shared" si="50"/>
+      <c r="Y32" s="10">
+        <f t="shared" si="45"/>
         <v>7.9284881461329171E-2</v>
       </c>
-      <c r="V32" s="10">
-        <f t="shared" si="50"/>
-        <v>5.8549393830272356E-2</v>
-      </c>
-      <c r="W32" s="10">
-        <f t="shared" si="50"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="X32" s="10">
-        <f t="shared" si="50"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="Y32" s="10">
-        <f t="shared" si="50"/>
+      <c r="Z32" s="10">
+        <f t="shared" si="45"/>
+        <v>3.0728604009122584E-2</v>
+      </c>
+      <c r="AA32" s="10">
+        <f t="shared" si="45"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="Z32" s="10">
-        <f t="shared" si="50"/>
+      <c r="AB32" s="10">
+        <f t="shared" si="45"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC32" s="10">
+        <f t="shared" si="45"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AD32" s="10">
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AA32" s="10">
-        <f t="shared" si="50"/>
+      <c r="AE32" s="10">
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB32" s="10">
-        <f t="shared" si="50"/>
+      <c r="AF32" s="10">
+        <f t="shared" si="45"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AC32" s="10">
-        <f t="shared" si="50"/>
+      <c r="AG32" s="10">
+        <f t="shared" si="45"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AD32" s="10">
-        <f t="shared" si="50"/>
+      <c r="AH32" s="10">
+        <f t="shared" si="45"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AE32" s="10">
-        <f t="shared" si="50"/>
+      <c r="AI32" s="10">
+        <f t="shared" si="45"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF32" s="10">
-        <f t="shared" si="50"/>
+      <c r="AJ32" s="10">
+        <f t="shared" si="45"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D33" s="10">
-        <f t="shared" ref="D33:J33" si="51">D15/D13</f>
+        <f t="shared" ref="D33:J33" si="46">D15/D13</f>
         <v>0.14773319437206878</v>
       </c>
       <c r="E33" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>0.14970670747258352</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>0.16050314465408805</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>0.17061955469506293</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>0.18186157517899762</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>0.15876288659793814</v>
       </c>
       <c r="K33" s="10">
@@ -3744,93 +3926,97 @@
         <v>0.17832744405182568</v>
       </c>
       <c r="L33" s="10">
-        <f t="shared" ref="L33:N33" si="52">L15/L13</f>
+        <f t="shared" ref="L33:N33" si="47">L15/L13</f>
         <v>0.1838702092640489</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>0.18371000223763706</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="52"/>
-        <v>0.17</v>
-      </c>
-      <c r="P33" s="10">
-        <f>P15/P13</f>
+        <f t="shared" si="47"/>
+        <v>0.17565961492750179</v>
+      </c>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="T33" s="10">
+        <f>T15/T13</f>
         <v>0.13953488372093023</v>
       </c>
-      <c r="Q33" s="10">
-        <f>Q15/Q13</f>
+      <c r="U33" s="10">
+        <f>U15/U13</f>
         <v>0.14125396438155649</v>
       </c>
-      <c r="R33" s="10">
-        <f t="shared" ref="R33:AF33" si="53">R15/R13</f>
+      <c r="V33" s="10">
+        <f t="shared" ref="V33:AJ33" si="48">V15/V13</f>
         <v>0.14661134163208853</v>
       </c>
-      <c r="S33" s="10">
-        <f t="shared" si="53"/>
+      <c r="W33" s="10">
+        <f t="shared" si="48"/>
         <v>0.14476243400944708</v>
       </c>
-      <c r="T33" s="10">
-        <f t="shared" si="53"/>
+      <c r="X33" s="10">
+        <f t="shared" si="48"/>
         <v>0.14535561601243685</v>
       </c>
-      <c r="U33" s="10">
-        <f t="shared" si="53"/>
+      <c r="Y33" s="10">
+        <f t="shared" si="48"/>
         <v>0.16792701956547834</v>
       </c>
-      <c r="V33" s="10">
-        <f t="shared" si="53"/>
-        <v>0.17882265394003127</v>
-      </c>
-      <c r="W33" s="10">
-        <f t="shared" si="53"/>
+      <c r="Z33" s="10">
+        <f t="shared" si="48"/>
+        <v>0.18044718760917666</v>
+      </c>
+      <c r="AA33" s="10">
+        <f t="shared" si="48"/>
         <v>0.18</v>
       </c>
-      <c r="X33" s="10">
-        <f t="shared" si="53"/>
+      <c r="AB33" s="10">
+        <f t="shared" si="48"/>
         <v>0.18</v>
       </c>
-      <c r="Y33" s="10">
-        <f t="shared" si="53"/>
+      <c r="AC33" s="10">
+        <f t="shared" si="48"/>
         <v>0.18</v>
       </c>
-      <c r="Z33" s="10">
-        <f t="shared" si="53"/>
+      <c r="AD33" s="10">
+        <f t="shared" si="48"/>
         <v>0.18</v>
       </c>
-      <c r="AA33" s="10">
-        <f t="shared" si="53"/>
+      <c r="AE33" s="10">
+        <f t="shared" si="48"/>
         <v>0.18</v>
       </c>
-      <c r="AB33" s="10">
-        <f t="shared" si="53"/>
+      <c r="AF33" s="10">
+        <f t="shared" si="48"/>
         <v>0.18</v>
       </c>
-      <c r="AC33" s="10">
-        <f t="shared" si="53"/>
+      <c r="AG33" s="10">
+        <f t="shared" si="48"/>
         <v>0.18</v>
       </c>
-      <c r="AD33" s="10">
-        <f t="shared" si="53"/>
+      <c r="AH33" s="10">
+        <f t="shared" si="48"/>
         <v>0.18</v>
       </c>
-      <c r="AE33" s="10">
-        <f t="shared" si="53"/>
+      <c r="AI33" s="10">
+        <f t="shared" si="48"/>
         <v>0.18</v>
       </c>
-      <c r="AF33" s="10">
-        <f t="shared" si="53"/>
+      <c r="AJ33" s="10">
+        <f t="shared" si="48"/>
         <v>0.18</v>
       </c>
-      <c r="AH33" s="1" t="s">
+      <c r="AL33" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AI33" s="10">
+      <c r="AM33" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>42</v>
       </c>
@@ -3839,11 +4025,11 @@
       <c r="F34" s="10"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10">
-        <f t="shared" ref="H34:I34" si="54">H16/D16-1</f>
+        <f t="shared" ref="H34:I34" si="49">H16/D16-1</f>
         <v>-2.5316455696202556E-2</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>3.3472803347280422E-2</v>
       </c>
       <c r="J34" s="10"/>
@@ -3852,116 +4038,120 @@
         <v>1.7699115044247815E-2</v>
       </c>
       <c r="L34" s="10">
-        <f t="shared" ref="L34:N34" si="55">L16/H16-1</f>
+        <f t="shared" ref="L34:N34" si="50">L16/H16-1</f>
         <v>-6.0606060606060552E-2</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>0.15789473684210531</v>
       </c>
       <c r="N34" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
+        <v>-4.6594982078853042E-2</v>
+      </c>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10">
+        <f>U16/T16-1</f>
+        <v>8.1664098613251079E-2</v>
+      </c>
+      <c r="V34" s="10">
+        <f t="shared" ref="V34:AJ34" si="51">V16/U16-1</f>
+        <v>0.21225071225071224</v>
+      </c>
+      <c r="W34" s="10">
+        <f t="shared" si="51"/>
+        <v>0.11750881316098716</v>
+      </c>
+      <c r="X34" s="10">
+        <f t="shared" si="51"/>
+        <v>-9.4637223974763929E-3</v>
+      </c>
+      <c r="Y34" s="10">
+        <f t="shared" si="51"/>
+        <v>4.3524416135881205E-2</v>
+      </c>
+      <c r="Z34" s="10">
+        <f t="shared" si="51"/>
+        <v>1.6276703967446515E-2</v>
+      </c>
+      <c r="AA34" s="10">
+        <f t="shared" si="51"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AB34" s="10">
+        <f t="shared" si="51"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AC34" s="10">
+        <f t="shared" si="51"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AD34" s="10">
+        <f t="shared" si="51"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE34" s="10">
+        <f t="shared" si="51"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF34" s="10">
+        <f t="shared" si="51"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10">
-        <f>Q16/P16-1</f>
-        <v>8.1664098613251079E-2</v>
-      </c>
-      <c r="R34" s="10">
-        <f t="shared" ref="R34:AF34" si="56">R16/Q16-1</f>
-        <v>0.21225071225071224</v>
-      </c>
-      <c r="S34" s="10">
-        <f t="shared" si="56"/>
-        <v>0.11750881316098716</v>
-      </c>
-      <c r="T34" s="10">
-        <f t="shared" si="56"/>
-        <v>-9.4637223974763929E-3</v>
-      </c>
-      <c r="U34" s="10">
-        <f t="shared" si="56"/>
-        <v>4.3524416135881205E-2</v>
-      </c>
-      <c r="V34" s="10">
-        <f t="shared" si="56"/>
-        <v>3.2339776195320358E-2</v>
-      </c>
-      <c r="W34" s="10">
-        <f t="shared" si="56"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="X34" s="10">
-        <f t="shared" si="56"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="Y34" s="10">
-        <f t="shared" si="56"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="Z34" s="10">
-        <f t="shared" si="56"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AA34" s="10">
-        <f t="shared" si="56"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AB34" s="10">
-        <f t="shared" si="56"/>
+      <c r="AG34" s="10">
+        <f t="shared" si="51"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AC34" s="10">
-        <f t="shared" si="56"/>
+      <c r="AH34" s="10">
+        <f t="shared" si="51"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AD34" s="10">
-        <f t="shared" si="56"/>
+      <c r="AI34" s="10">
+        <f t="shared" si="51"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AE34" s="10">
-        <f t="shared" si="56"/>
+      <c r="AJ34" s="10">
+        <f t="shared" si="51"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF34" s="10">
-        <f t="shared" si="56"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AH34" s="1" t="s">
+      <c r="AL34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AI34" s="10">
+      <c r="AM34" s="10">
         <v>0.08</v>
       </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D35" s="10">
-        <f t="shared" ref="D35:J35" si="57">D16/D13</f>
+        <f t="shared" ref="D35:J35" si="52">D16/D13</f>
         <v>6.175091193329859E-2</v>
       </c>
       <c r="E35" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>6.0953838306554452E-2</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>5.6855345911949684E-2</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>5.5905130687318491E-2</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>5.8949880668257758E-2</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>6.3917525773195871E-2</v>
       </c>
       <c r="K35" s="10">
@@ -3969,120 +4159,124 @@
         <v>5.418138987043581E-2</v>
       </c>
       <c r="L35" s="10">
-        <f t="shared" ref="L35:N35" si="58">L16/L13</f>
+        <f t="shared" ref="L35:N35" si="53">L16/L13</f>
         <v>5.1022807430049374E-2</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="53"/>
         <v>6.3996419780711564E-2</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="58"/>
-        <v>6.033336544946527E-2</v>
-      </c>
-      <c r="P35" s="10">
-        <f>P16/P13</f>
+        <f t="shared" si="53"/>
+        <v>6.3227953410981697E-2</v>
+      </c>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="T35" s="10">
+        <f>T16/T13</f>
         <v>5.8500090138813771E-2</v>
       </c>
-      <c r="Q35" s="10">
-        <f>Q16/Q13</f>
+      <c r="U35" s="10">
+        <f>U16/U13</f>
         <v>5.7087094413271533E-2</v>
       </c>
-      <c r="R35" s="10">
-        <f t="shared" ref="R35:AF35" si="59">R16/R13</f>
+      <c r="V35" s="10">
+        <f t="shared" ref="V35:AJ35" si="54">V16/V13</f>
         <v>6.1949479507898378E-2</v>
       </c>
-      <c r="S35" s="10">
-        <f t="shared" si="59"/>
+      <c r="W35" s="10">
+        <f t="shared" si="54"/>
         <v>6.6060016671297586E-2</v>
       </c>
-      <c r="T35" s="10">
-        <f t="shared" si="59"/>
+      <c r="X35" s="10">
+        <f t="shared" si="54"/>
         <v>6.1018266614846481E-2</v>
       </c>
-      <c r="U35" s="10">
-        <f t="shared" si="59"/>
+      <c r="Y35" s="10">
+        <f t="shared" si="54"/>
         <v>5.8996519025327092E-2</v>
       </c>
-      <c r="V35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.7535768856785664E-2</v>
-      </c>
-      <c r="W35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.5891889746591789E-2</v>
-      </c>
-      <c r="X35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.4817045713003484E-2</v>
-      </c>
-      <c r="Y35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.428484138569277E-2</v>
-      </c>
       <c r="Z35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.4284841385692777E-2</v>
+        <f t="shared" si="54"/>
+        <v>5.8169325724933038E-2</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.4284841385692784E-2</v>
+        <f t="shared" si="54"/>
+        <v>5.7604574989739511E-2</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.4284841385692791E-2</v>
+        <f t="shared" si="54"/>
+        <v>5.704530727139253E-2</v>
       </c>
       <c r="AC35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.4284841385692784E-2</v>
+        <f t="shared" si="54"/>
+        <v>5.6491469336718815E-2</v>
       </c>
       <c r="AD35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.4284841385692791E-2</v>
+        <f t="shared" si="54"/>
+        <v>5.6491469336718808E-2</v>
       </c>
       <c r="AE35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.4284841385692791E-2</v>
+        <f t="shared" si="54"/>
+        <v>5.6491469336718815E-2</v>
       </c>
       <c r="AF35" s="10">
-        <f t="shared" si="59"/>
-        <v>5.4284841385692791E-2</v>
-      </c>
-      <c r="AH35" s="1" t="s">
+        <f t="shared" si="54"/>
+        <v>5.6491469336718822E-2</v>
+      </c>
+      <c r="AG35" s="10">
+        <f t="shared" si="54"/>
+        <v>5.6491469336718815E-2</v>
+      </c>
+      <c r="AH35" s="10">
+        <f t="shared" si="54"/>
+        <v>5.6491469336718815E-2</v>
+      </c>
+      <c r="AI35" s="10">
+        <f t="shared" si="54"/>
+        <v>5.6491469336718822E-2</v>
+      </c>
+      <c r="AJ35" s="10">
+        <f t="shared" si="54"/>
+        <v>5.6491469336718815E-2</v>
+      </c>
+      <c r="AL35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AI35" s="6">
-        <f>NPV(AI34,V28:EM28)</f>
-        <v>21577.850136476831</v>
-      </c>
-    </row>
-    <row r="36" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AM35" s="6">
+        <f>NPV(AM34,Z28:EQ28)</f>
+        <v>19927.575722691061</v>
+      </c>
+    </row>
+    <row r="36" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D36" s="10">
-        <f t="shared" ref="D36:J36" si="60">D20/D13</f>
+        <f t="shared" ref="D36:J36" si="55">D20/D13</f>
         <v>8.4418968212610732E-2</v>
       </c>
       <c r="E36" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="55"/>
         <v>-8.7732721244580467E-2</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="55"/>
         <v>0.10264150943396226</v>
       </c>
       <c r="H36" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="55"/>
         <v>0.11302032913843175</v>
       </c>
       <c r="I36" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="55"/>
         <v>0.12076372315035799</v>
       </c>
       <c r="J36" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="55"/>
         <v>9.3241695303550975E-2</v>
       </c>
       <c r="K36" s="10">
@@ -4090,120 +4284,124 @@
         <v>0.1232037691401649</v>
       </c>
       <c r="L36" s="10">
-        <f t="shared" ref="L36:N36" si="61">L20/L13</f>
+        <f t="shared" ref="L36:N36" si="56">L20/L13</f>
         <v>0.13237714554432164</v>
       </c>
       <c r="M36" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="56"/>
         <v>0.11792347281270978</v>
       </c>
       <c r="N36" s="10">
-        <f t="shared" si="61"/>
-        <v>0.10881020436565286</v>
-      </c>
-      <c r="P36" s="10">
-        <f>P20/P13</f>
+        <f t="shared" si="56"/>
+        <v>0.11029236985975754</v>
+      </c>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="T36" s="10">
+        <f>T20/T13</f>
         <v>8.0584099513250407E-2</v>
       </c>
-      <c r="Q36" s="10">
-        <f>Q20/Q13</f>
+      <c r="U36" s="10">
+        <f>U20/U13</f>
         <v>8.0019516955354961E-2</v>
       </c>
-      <c r="R36" s="10">
-        <f t="shared" ref="R36:AF36" si="62">R20/R13</f>
+      <c r="V36" s="10">
+        <f t="shared" ref="V36:AJ36" si="57">V20/V13</f>
         <v>8.2405183082186792E-2</v>
       </c>
-      <c r="S36" s="10">
-        <f t="shared" si="62"/>
+      <c r="W36" s="10">
+        <f t="shared" si="57"/>
         <v>7.4742984162267295E-2</v>
       </c>
-      <c r="T36" s="10">
-        <f t="shared" si="62"/>
+      <c r="X36" s="10">
+        <f t="shared" si="57"/>
         <v>3.8282160901671199E-2</v>
       </c>
-      <c r="U36" s="10">
-        <f t="shared" si="62"/>
+      <c r="Y36" s="10">
+        <f t="shared" si="57"/>
         <v>0.10731004681310767</v>
       </c>
-      <c r="V36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12026633517693777</v>
-      </c>
-      <c r="W36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12334458773091123</v>
-      </c>
-      <c r="X36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12444145645264847</v>
-      </c>
-      <c r="Y36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12498805879616014</v>
-      </c>
       <c r="Z36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12499518722574982</v>
+        <f t="shared" si="57"/>
+        <v>0.12093862815884476</v>
       </c>
       <c r="AA36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12500224576877486</v>
+        <f t="shared" si="57"/>
+        <v>0.12136768042909747</v>
       </c>
       <c r="AB36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12500224576877486</v>
+        <f t="shared" si="57"/>
+        <v>0.12194690435290396</v>
       </c>
       <c r="AC36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12500224576877486</v>
+        <f t="shared" si="57"/>
+        <v>0.122520310993902</v>
       </c>
       <c r="AD36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12500224576877486</v>
+        <f t="shared" si="57"/>
+        <v>0.12252999942203317</v>
       </c>
       <c r="AE36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12500224576877483</v>
+        <f t="shared" si="57"/>
+        <v>0.12253959286557481</v>
       </c>
       <c r="AF36" s="10">
-        <f t="shared" si="62"/>
-        <v>0.12500224576877489</v>
-      </c>
-      <c r="AH36" s="1" t="s">
+        <f t="shared" si="57"/>
+        <v>0.12253959286557481</v>
+      </c>
+      <c r="AG36" s="10">
+        <f t="shared" si="57"/>
+        <v>0.1225395928655748</v>
+      </c>
+      <c r="AH36" s="10">
+        <f t="shared" si="57"/>
+        <v>0.12253959286557481</v>
+      </c>
+      <c r="AI36" s="10">
+        <f t="shared" si="57"/>
+        <v>0.12253959286557481</v>
+      </c>
+      <c r="AJ36" s="10">
+        <f t="shared" si="57"/>
+        <v>0.12253959286557482</v>
+      </c>
+      <c r="AL36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI36" s="6">
+      <c r="AM36" s="6">
         <f>Main!D8</f>
-        <v>-3677</v>
-      </c>
-    </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.3">
+        <v>-3540</v>
+      </c>
+    </row>
+    <row r="37" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D37" s="10">
-        <f t="shared" ref="D37:J37" si="63">D26/D25</f>
+        <f t="shared" ref="D37:J37" si="58">D26/D25</f>
         <v>0.23357664233576642</v>
       </c>
       <c r="E37" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>-2.0618556701030927E-2</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.23097826086956522</v>
       </c>
       <c r="H37" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.23943661971830985</v>
       </c>
       <c r="I37" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.22978723404255319</v>
       </c>
       <c r="J37" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.248</v>
       </c>
       <c r="K37" s="10">
@@ -4211,120 +4409,124 @@
         <v>0.23640167364016737</v>
       </c>
       <c r="L37" s="10">
-        <f t="shared" ref="L37:N37" si="64">L26/L25</f>
+        <f t="shared" ref="L37:N37" si="59">L26/L25</f>
         <v>0.2413127413127413</v>
       </c>
       <c r="M37" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>0.23760330578512398</v>
       </c>
       <c r="N37" s="10">
-        <f t="shared" si="64"/>
-        <v>0.22000000000000003</v>
-      </c>
-      <c r="P37" s="10">
-        <f>P26/P25</f>
+        <f t="shared" si="59"/>
+        <v>0.21911421911421911</v>
+      </c>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="T37" s="10">
+        <f>T26/T25</f>
         <v>0.22632794457274827</v>
       </c>
-      <c r="Q37" s="10">
-        <f>Q26/Q25</f>
+      <c r="U37" s="10">
+        <f>U26/U25</f>
         <v>0.1946222791293214</v>
       </c>
-      <c r="R37" s="10">
-        <f t="shared" ref="R37:AF37" si="65">R26/R25</f>
+      <c r="V37" s="10">
+        <f t="shared" ref="V37:AJ37" si="60">V26/V25</f>
         <v>0.21509824198552224</v>
       </c>
-      <c r="S37" s="10">
-        <f t="shared" si="65"/>
+      <c r="W37" s="10">
+        <f t="shared" si="60"/>
         <v>0.21783295711060949</v>
       </c>
-      <c r="T37" s="10">
-        <f t="shared" si="65"/>
+      <c r="X37" s="10">
+        <f t="shared" si="60"/>
         <v>0.4838709677419355</v>
       </c>
-      <c r="U37" s="10">
-        <f t="shared" si="65"/>
+      <c r="Y37" s="10">
+        <f t="shared" si="60"/>
         <v>0.23672971323978034</v>
       </c>
-      <c r="V37" s="10">
-        <f t="shared" si="65"/>
-        <v>0.23403240307207215</v>
-      </c>
-      <c r="W37" s="10">
-        <f t="shared" si="65"/>
+      <c r="Z37" s="10">
+        <f t="shared" si="60"/>
+        <v>0.23415400733368255</v>
+      </c>
+      <c r="AA37" s="10">
+        <f t="shared" si="60"/>
         <v>0.23</v>
       </c>
-      <c r="X37" s="10">
-        <f t="shared" si="65"/>
+      <c r="AB37" s="10">
+        <f t="shared" si="60"/>
         <v>0.23</v>
       </c>
-      <c r="Y37" s="10">
-        <f t="shared" si="65"/>
+      <c r="AC37" s="10">
+        <f t="shared" si="60"/>
         <v>0.23</v>
       </c>
-      <c r="Z37" s="10">
-        <f t="shared" si="65"/>
+      <c r="AD37" s="10">
+        <f t="shared" si="60"/>
         <v>0.23</v>
       </c>
-      <c r="AA37" s="10">
-        <f t="shared" si="65"/>
+      <c r="AE37" s="10">
+        <f t="shared" si="60"/>
+        <v>0.23</v>
+      </c>
+      <c r="AF37" s="10">
+        <f t="shared" si="60"/>
+        <v>0.23</v>
+      </c>
+      <c r="AG37" s="10">
+        <f t="shared" si="60"/>
         <v>0.22999999999999998</v>
       </c>
-      <c r="AB37" s="10">
-        <f t="shared" si="65"/>
+      <c r="AH37" s="10">
+        <f t="shared" si="60"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="AI37" s="10">
+        <f t="shared" si="60"/>
         <v>0.23</v>
       </c>
-      <c r="AC37" s="10">
-        <f t="shared" si="65"/>
+      <c r="AJ37" s="10">
+        <f t="shared" si="60"/>
         <v>0.23</v>
       </c>
-      <c r="AD37" s="10">
-        <f t="shared" si="65"/>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="AE37" s="10">
-        <f t="shared" si="65"/>
-        <v>0.23</v>
-      </c>
-      <c r="AF37" s="10">
-        <f t="shared" si="65"/>
-        <v>0.23000000000000004</v>
-      </c>
-      <c r="AH37" s="1" t="s">
+      <c r="AL37" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AI37" s="6">
-        <f>AI35+AI36</f>
-        <v>17900.850136476831</v>
-      </c>
-    </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AM37" s="6">
+        <f>AM35+AM36</f>
+        <v>16387.575722691061</v>
+      </c>
+    </row>
+    <row r="38" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D38" s="10">
-        <f t="shared" ref="D38:J38" si="66">D28/D13</f>
+        <f t="shared" ref="D38:J38" si="61">D28/D13</f>
         <v>5.3934340802501306E-2</v>
       </c>
       <c r="E38" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="61"/>
         <v>-0.10175975516449885</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="61"/>
         <v>7.1446540880503145E-2</v>
       </c>
       <c r="H38" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="61"/>
         <v>7.7928363988383348E-2</v>
       </c>
       <c r="I38" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="61"/>
         <v>8.6873508353221954E-2</v>
       </c>
       <c r="J38" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="61"/>
         <v>6.5063001145475377E-2</v>
       </c>
       <c r="K38" s="10">
@@ -4332,120 +4534,124 @@
         <v>8.5512367491166072E-2</v>
       </c>
       <c r="L38" s="10">
-        <f t="shared" ref="L38:N38" si="67">L28/L13</f>
+        <f t="shared" ref="L38:N38" si="62">L28/L13</f>
         <v>9.193510463202445E-2</v>
       </c>
       <c r="M38" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="62"/>
         <v>8.2121279928395616E-2</v>
       </c>
       <c r="N38" s="10">
-        <f t="shared" si="67"/>
-        <v>7.8929961139480365E-2</v>
-      </c>
-      <c r="P38" s="10">
-        <f>P28/P13</f>
+        <f t="shared" si="62"/>
+        <v>7.7727596862372239E-2</v>
+      </c>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="T38" s="10">
+        <f>T28/T13</f>
         <v>6.0122588786731566E-2</v>
       </c>
-      <c r="Q38" s="10">
-        <f>Q28/Q13</f>
+      <c r="U38" s="10">
+        <f>U28/U13</f>
         <v>5.1069366512157439E-2</v>
       </c>
-      <c r="R38" s="10">
-        <f t="shared" ref="R38:AF38" si="68">R28/R13</f>
+      <c r="V38" s="10">
+        <f t="shared" ref="V38:AJ38" si="63">V28/V13</f>
         <v>5.4815461891242631E-2</v>
       </c>
-      <c r="S38" s="10">
-        <f t="shared" si="68"/>
+      <c r="W38" s="10">
+        <f t="shared" si="63"/>
         <v>4.7582661850514033E-2</v>
       </c>
-      <c r="T38" s="10">
-        <f t="shared" si="68"/>
+      <c r="X38" s="10">
+        <f t="shared" si="63"/>
         <v>1.28902707604612E-2</v>
       </c>
-      <c r="U38" s="10">
-        <f t="shared" si="68"/>
+      <c r="Y38" s="10">
+        <f t="shared" si="63"/>
         <v>7.5261073100468132E-2</v>
       </c>
-      <c r="V38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.4458801250740539E-2</v>
-      </c>
-      <c r="W38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.7798669127325882E-2</v>
-      </c>
-      <c r="X38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.8712264422154671E-2</v>
-      </c>
-      <c r="Y38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.9133148226658646E-2</v>
-      </c>
       <c r="Z38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.9068954205223233E-2</v>
+        <f t="shared" si="63"/>
+        <v>8.4313497146849894E-2</v>
       </c>
       <c r="AA38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.9004023205327007E-2</v>
+        <f t="shared" si="63"/>
+        <v>8.5786291990262969E-2</v>
       </c>
       <c r="AB38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.8860504273908611E-2</v>
+        <f t="shared" si="63"/>
+        <v>8.6232294411593968E-2</v>
       </c>
       <c r="AC38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.871414338345221E-2</v>
+        <f t="shared" si="63"/>
+        <v>8.6673817525162455E-2</v>
       </c>
       <c r="AD38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.8564884257541221E-2</v>
+        <f t="shared" si="63"/>
+        <v>8.6606112693841691E-2</v>
       </c>
       <c r="AE38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.8412669505374561E-2</v>
+        <f t="shared" si="63"/>
+        <v>8.6537597813396941E-2</v>
       </c>
       <c r="AF38" s="10">
-        <f t="shared" si="68"/>
-        <v>8.8257440599699685E-2</v>
-      </c>
-      <c r="AH38" s="1" t="s">
+        <f t="shared" si="63"/>
+        <v>8.6382788136305927E-2</v>
+      </c>
+      <c r="AG38" s="10">
+        <f t="shared" si="63"/>
+        <v>8.6224912921054719E-2</v>
+      </c>
+      <c r="AH38" s="10">
+        <f t="shared" si="63"/>
+        <v>8.6063911463917342E-2</v>
+      </c>
+      <c r="AI38" s="10">
+        <f t="shared" si="63"/>
+        <v>8.5899721859113862E-2</v>
+      </c>
+      <c r="AJ38" s="10">
+        <f t="shared" si="63"/>
+        <v>8.5732280975007347E-2</v>
+      </c>
+      <c r="AL38" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AI38" s="5">
-        <f>AI37/AF29-1</f>
-        <v>138.95973523437709</v>
-      </c>
-    </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="AH39" s="1" t="s">
+      <c r="AM38" s="5">
+        <f>AM37/AJ29-1</f>
+        <v>128.03602931252803</v>
+      </c>
+    </row>
+    <row r="39" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="AL39" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AI39" s="5">
+      <c r="AM39" s="5">
         <f>Main!D3</f>
-        <v>190.36</v>
-      </c>
-    </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="AH40" s="2" t="s">
+        <v>172.3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="AL40" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AI40" s="11">
-        <f>AI38/AI39-1</f>
-        <v>-0.27001609984042296</v>
-      </c>
-    </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="AH41" s="1" t="s">
+      <c r="AM40" s="11">
+        <f>AM38/AM39-1</f>
+        <v>-0.25690058437302365</v>
+      </c>
+    </row>
+    <row r="41" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="AL41" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AI41" s="7" t="s">
+      <c r="AM41" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="2:35" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:39" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B42" s="12" t="s">
         <v>56</v>
       </c>
@@ -4456,28 +4662,31 @@
       <c r="M42" s="14">
         <v>13542</v>
       </c>
-      <c r="V42" s="14">
+      <c r="N42" s="14">
         <v>13542</v>
       </c>
-    </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="Z42" s="14">
+        <v>13542</v>
+      </c>
+    </row>
+    <row r="44" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>57</v>
       </c>
       <c r="L44" s="13"/>
-      <c r="V44" s="13">
-        <f>Main!$D$9/Model!V42</f>
-        <v>2.0694169251218435</v>
-      </c>
-    </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="Z44" s="13">
+        <f>Main!$D$9/Model!Z42</f>
+        <v>1.8772780977699013</v>
+      </c>
+    </row>
+    <row r="45" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>58</v>
       </c>
       <c r="L45" s="10"/>
-      <c r="V45" s="10">
-        <f>V42/Main!$D$9-1</f>
-        <v>-0.51677209756022369</v>
+      <c r="Z45" s="10">
+        <f>Z42/Main!$D$9-1</f>
+        <v>-0.46731387257543633</v>
       </c>
     </row>
   </sheetData>
